--- a/docs/xlsx/jobs-2026-09-16.xlsx
+++ b/docs/xlsx/jobs-2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="627">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1870 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Air Resource Specialist</t>
+  </si>
+  <si>
+    <t>Puget Sound Clean Air Agency</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$109,197 - $139,336 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-air-resource-specialist-seattle-washington/6833590391</t>
+  </si>
+  <si>
+    <t>Crew Leader</t>
+  </si>
+  <si>
+    <t>Conservation Corps MN/IA</t>
+  </si>
+  <si>
+    <t>Various, MN</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$2,500 per month</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crew-leader-various-minnesota/6333775295</t>
+  </si>
+  <si>
+    <t>Crew Member</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crew-member-various-minnesota/8884919346</t>
+  </si>
+  <si>
+    <t>Data Center Fixed-Term Organizer</t>
+  </si>
+  <si>
+    <t>Stand.earth</t>
+  </si>
+  <si>
+    <t>United States, Remote</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$27.64 - $40.87 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-center-fixed-term-organizer-united-states-remote/6314498461</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Oregon Wild</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$70,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-manager-portland-oregon/3220572325</t>
+  </si>
+  <si>
+    <t>Director of Learning and Evaluation</t>
+  </si>
+  <si>
+    <t>Trust for Public Land</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$111,402 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-learning-and-evaluation-remote-remote/7066502846</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Animal Welfare Institute</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$95,000 - $135,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-operations-washington-dc/1741413395</t>
+  </si>
+  <si>
+    <t>Director of Philanthropy</t>
+  </si>
+  <si>
+    <t>Access Fund</t>
+  </si>
+  <si>
+    <t>Boulder, CO</t>
+  </si>
+  <si>
+    <t>$90,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-philanthropy-boulder-colorado/8551235700</t>
+  </si>
+  <si>
+    <t>Division of Marine Fisheries Management - Section Leader, Analysis &amp; Rulemaking Section</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>$85,939 - $92,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-division-of-marine-fisheries-management---section-leader-analysis--rulemaking-section-tallahassee-florida/7688672567</t>
+  </si>
+  <si>
+    <t>Environmental Geologist</t>
+  </si>
+  <si>
+    <t>North Wind Portage</t>
+  </si>
+  <si>
+    <t>Simi Valley, CA</t>
+  </si>
+  <si>
+    <t>$90,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-geologist-simi-valley-california/5867616039</t>
+  </si>
+  <si>
+    <t>Environmental Scientist</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Rancho Cordova, CA</t>
+  </si>
+  <si>
+    <t>$4,418 - $9,321 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-rancho-cordova-california/9977785411</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-los-angeles-california/3022389968</t>
+  </si>
+  <si>
+    <t>Facilities Manager</t>
+  </si>
+  <si>
+    <t>American Prairie</t>
+  </si>
+  <si>
+    <t>Lewistown, MT</t>
+  </si>
+  <si>
+    <t>$28 - $34.50 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-facilities-manager-lewistown-montana/9518535534</t>
+  </si>
+  <si>
+    <t>Field Crew Member</t>
+  </si>
+  <si>
+    <t>Des Moines, IA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-crew-member-des-moines-iowa/8744490664</t>
+  </si>
+  <si>
+    <t>Field Specialist</t>
+  </si>
+  <si>
+    <t>$2,600 per month</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-specialist-various-minnesota/1979565120</t>
+  </si>
+  <si>
+    <t>Fisheries Technician 1- American River Rotary Screw Traps</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$17.29 - $28.22 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-1--american-river-rotary-screw-traps-sacramento-california/3069328599</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife - OPS Biological Scientist II - Invasive Plants</t>
+  </si>
+  <si>
+    <t>$19.71 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-florida-fish-and-wildlife---ops-biological-scientist-ii---invasive-plants-tallahassee-florida/4479705720</t>
+  </si>
+  <si>
+    <t>Forester Senior (Multiple Positions)</t>
+  </si>
+  <si>
+    <t>WI DNR Division of Forestry</t>
+  </si>
+  <si>
+    <t>Varies, WI</t>
+  </si>
+  <si>
+    <t>$32.68 - $36.43 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forester-senior-multiple-positions-varies-wisconsin/6074689940</t>
+  </si>
+  <si>
+    <t>Full Time Field Biologist</t>
+  </si>
+  <si>
+    <t>Santa Ana Watershed Association</t>
+  </si>
+  <si>
+    <t>Riverside, CA</t>
+  </si>
+  <si>
+    <t>$25.79 - $33.01 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-full-time-field-biologist-riverside-california/6420550305</t>
+  </si>
+  <si>
+    <t>Gila Agreements Project Coordinator</t>
+  </si>
+  <si>
+    <t>Bat Conservation International Inc.</t>
+  </si>
+  <si>
+    <t>Silver City, NM</t>
+  </si>
+  <si>
+    <t>$55,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gila-agreements-project-coordinator-silver-city-new-mexico/3270412132</t>
+  </si>
+  <si>
+    <t>Manager of Human Resources</t>
+  </si>
+  <si>
+    <t>$80,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-manager-of-human-resources-washington-dc/1249483527</t>
+  </si>
+  <si>
+    <t>Native Seeds Coordinator (BLM, Multiple Locations)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>$35.00/hr</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-native-seeds-coordinator-blm--multiple-locations-remote-remote/9503550094</t>
+  </si>
+  <si>
+    <t>Nature-Based Educator</t>
+  </si>
+  <si>
+    <t>Center for Wildlife</t>
+  </si>
+  <si>
+    <t>Cape Neddick, ME</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nature-based-educator-cape-neddick-maine/7378969492</t>
+  </si>
+  <si>
+    <t>Office Assistant</t>
+  </si>
+  <si>
+    <t>Friends of the Elephant Seal</t>
+  </si>
+  <si>
+    <t>San Simeon, CA</t>
+  </si>
+  <si>
+    <t>$22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-office-assistant-san-simeon-california/7830627903</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Wild Virginia</t>
+  </si>
+  <si>
+    <t>Charlottesville, Remote</t>
+  </si>
+  <si>
+    <t>$40,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-coordinator-charlottesville-remote/1768008278</t>
+  </si>
+  <si>
+    <t>Planning and Recreation Section Manager - Environmental Planner 5 - Permanent - 2026-07639</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$7,044 - $9,478 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-planning-and-recreation-section-manager---environmental-planner-5---permanent---2026-07639-olympia-washington/9859969084</t>
+  </si>
+  <si>
+    <t>Postdoctoral Research Associate</t>
+  </si>
+  <si>
+    <t>University of Oklahoma</t>
+  </si>
+  <si>
+    <t>Norman, OK</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Salary commensurate with experience ($60-65K per year)</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-research-associate-norman-oklahoma/2091246432</t>
+  </si>
+  <si>
+    <t>The Arizona Institute for Resilience, University of Arizona</t>
+  </si>
+  <si>
+    <t>Tucson, AZ</t>
+  </si>
+  <si>
+    <t>NIH salary guidelines, Depends on Experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-research-associate-tucson-arizona/5319652570</t>
+  </si>
+  <si>
+    <t>Regional Manger</t>
+  </si>
+  <si>
+    <t>HAWKs Los Angeles</t>
+  </si>
+  <si>
+    <t>$100,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-manger-los-angeles-california/5034262759</t>
+  </si>
+  <si>
+    <t>Scientific Aid</t>
+  </si>
+  <si>
+    <t>$18.26 - $21.67 per hour</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-scientific-aid-rancho-cordova-california/1296973430</t>
+  </si>
+  <si>
+    <t>Seasonal Forestry Technician (6 Months)</t>
+  </si>
+  <si>
+    <t>CEMML</t>
+  </si>
+  <si>
+    <t>Fort McCoy, WI</t>
+  </si>
+  <si>
+    <t>$18.50 - $20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-forestry-technician-6-months-fort-mccoy-wisconsin/8737367897</t>
+  </si>
+  <si>
+    <t>Senior Environmental Scientist (Supervisory)</t>
+  </si>
+  <si>
+    <t>$10,854 - $13,493 per month</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-environmental-scientist-supervisory-sacramento-california/6134552745</t>
+  </si>
+  <si>
+    <t>Senior Trail Leader</t>
+  </si>
+  <si>
+    <t>Maine Conservation Corps</t>
+  </si>
+  <si>
+    <t>Augusta, ME</t>
+  </si>
+  <si>
+    <t>$620 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-trail-leader-augusta-maine/5324165269</t>
+  </si>
+  <si>
+    <t>Senior Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>$11,437 - $14,315 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-water-resource-control-engineer-los-angeles-california/8839478570</t>
+  </si>
+  <si>
+    <t>Southeast California Section Chief</t>
+  </si>
+  <si>
+    <t>San Bernardino, CA</t>
+  </si>
+  <si>
+    <t>$12,562 - $15,724 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southeast-california-section-chief-san-bernardino-california/8680318462</t>
+  </si>
+  <si>
+    <t>State Program Coordinator</t>
+  </si>
+  <si>
+    <t>Portland or Eugene, OR</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-program-coordinator-portland-or-eugene-oregon/2658481435</t>
+  </si>
+  <si>
+    <t>Stengl-Wyer Postdoctoral Scholars in Biodiversity Sciences - UT Austin</t>
+  </si>
+  <si>
+    <t>The University of Texas at Austin</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$70,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stengl-wyer-postdoctoral-scholars-in-biodiversity-sciences---ut-austin-austin-texas/8464968599</t>
+  </si>
+  <si>
+    <t>TWDB - 26-107 Regional Water Planner (Planner II-III)</t>
+  </si>
+  <si>
+    <t>Texas Water Development Board</t>
+  </si>
+  <si>
+    <t>$5,165 - $5,733.96 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---26-107-regional-water-planner-planner-ii-iii-austin-texas/5029350266</t>
+  </si>
+  <si>
+    <t>TWDB - 26-123 Recorder Program Geoscientist (Geoscientist II)</t>
+  </si>
+  <si>
+    <t>$6,000 - $6,666.67 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---26-123-recorder-program-geoscientist-geoscientist-ii-austin-texas/6057490574</t>
+  </si>
+  <si>
+    <t>TWDB - 26-124 Water Resources Engineer (Engineer II-V or Project Manager II-IV)</t>
+  </si>
+  <si>
+    <t>$6,100 - $8,610 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---26-124-water-resources-engineer-engineer-ii-v-or-project-manager-ii-iv-austin-texas/5660021385</t>
+  </si>
+  <si>
+    <t>TWDB - 26-125 Recorder Program Specialist (Hydrologist I)</t>
+  </si>
+  <si>
+    <t>$4,500 - $4,666.67 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---26-125-recorder-program-specialist-hydrologist-i-austin-texas/9256360827</t>
+  </si>
+  <si>
+    <t>Vegetation Information System Specialist</t>
+  </si>
+  <si>
+    <t>Natural Resource Services, Inc.</t>
+  </si>
+  <si>
+    <t>Sauk Rapids, MN</t>
+  </si>
+  <si>
+    <t>$25 - $28 per hour</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vegetation-information-system-specialist-sauk-rapids-minnesota/5556238502</t>
+  </si>
+  <si>
+    <t>Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>San Luis Obispo, CA</t>
+  </si>
+  <si>
+    <t>$6,488 - $12,152 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-san-luis-obispo-california/7649697860</t>
+  </si>
+  <si>
+    <t>Wildland Fire and Forest Health Engine Boss</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>East Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>$50,412 - $67,704 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-and-forest-health-engine-boss-east-wenatchee-washington/7691312896</t>
+  </si>
+  <si>
+    <t>Wildland Fire Hand Crew Squad Boss</t>
+  </si>
+  <si>
+    <t>Cle Elum, WA</t>
+  </si>
+  <si>
+    <t>$45,924 - $61,332 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-hand-crew-squad-boss-cle-elum-washington/6538224481</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Advocate - Urban Wildlands</t>
+  </si>
+  <si>
+    <t>Center for Biological Diversity</t>
+  </si>
+  <si>
+    <t>Remote, California (SF Bay Area, Sacramento, or LA preferred), CA</t>
+  </si>
+  <si>
+    <t>$63,600 - $91,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-conservation-advocate---urban-wildlands-remote-california-sf-bay-area-sacramento-or-la-preferred-california/4787084620</t>
+  </si>
+  <si>
+    <t>Youth Education Specialist</t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-youth-education-specialist-minneapolis-minnesota/3172449921</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>De Novo Center For Justice and Healing</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f598568af6c4a8681f911515fe34098-administrative-assistant-de-novo-center-for-justice-and-healing-cambridge</t>
+  </si>
+  <si>
+    <t>Administrative Specialist - Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 30.92 - 40.13/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e34fcdd04ed74aab90457019baffb106-administrative-specialist-personnel-and-human-resources-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Advocacy &amp; Organizing Manager</t>
+  </si>
+  <si>
+    <t>Northwest Community Bail Fund</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ef553a8d79c4fb28366cb3d3ce565eb-advocacy-organizing-manager-northwest-community-bail-fund-seattle</t>
+  </si>
+  <si>
+    <t>Alternatives to Violence Project New York Office Adminstrator</t>
+  </si>
+  <si>
+    <t>ALTERNATIVES TO VIOLENCE PROJECT INC</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/010ffb912109499d8d95709eb818d1fb-alternatives-to-violence-project-new-york-office-adminstrator-alternatives-to-violence-project-inc-ithaca</t>
+  </si>
+  <si>
+    <t>Analista de Projetos Pleno - Vaga Exclusivamente para pessoas negras e indígenas</t>
+  </si>
+  <si>
+    <t>Instituto Brasileiro de Defesa do Consumidor</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Policy, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61d571006330475e9726d251e51c83d0-analista-de-projetos-pleno-vaga-exclusivamente-para-pessoas-negras-e-indigenas-instituto-brasileiro-de-defesa-do-consumidor-sao-paulo</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General, Consumer Frauds Bureau (3912)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 91506.00 - 190643.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d1d9699b08dd42d18eba107c6bd33f56-assistant-attorney-general-consumer-frauds-bureau-3912-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General: Environmental Protection (3911)</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/ace2a0508efc4815b89bab1e668be1e0-assistant-attorney-general-environmental-protection-3911-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
+    <t>Assistant Director - Caregiver Program</t>
+  </si>
+  <si>
+    <t>Greenwich House, Inc.</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 71440.00 - 71440.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87d982ceac3e4026bb634135d963f6bd-assistant-director-caregiver-program-greenwich-house-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Assistant Director, Programs and Student Leadership</t>
+  </si>
+  <si>
+    <t>Bentley University</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 53889.00 - 86674.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5fbe6eadfaf4438b972d84cbbf75418e-assistant-director-programs-and-student-leadership-bentley-university-waltham</t>
+  </si>
+  <si>
+    <t>Audience Engagement Manager</t>
+  </si>
+  <si>
+    <t>Critical Path Advisors</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a67235c85be540e2a55468b2a4f8d58b-audience-engagement-manager-critical-path-advisors-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Paralegal</t>
+  </si>
+  <si>
+    <t>A Safe Place</t>
+  </si>
+  <si>
+    <t>Waukegan, Illinois</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/044f08ccb6484ad185381f8a035449a5-bilingual-paralegal-a-safe-place-waukegan</t>
+  </si>
+  <si>
+    <t>Billing Specialist</t>
+  </si>
+  <si>
+    <t>Veterans Inc.</t>
+  </si>
+  <si>
+    <t>Shrewsbury, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 26.44 - 31.25/hour</t>
+  </si>
+  <si>
+    <t>Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac800d39f29b4d67868681dca6167059-billing-specialist-veterans-inc-shrewsbury</t>
+  </si>
+  <si>
+    <t>Care Companion to Adults with Developmental Disabilities in Intentional Community</t>
+  </si>
+  <si>
+    <t>L'Arche Noah Sealth of Seattle</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 21.30 - 21.30/hour</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4ccd5958e3b4b37832c1fa866627001-care-companion-to-adults-with-developmental-disabilities-in-intentional-community-larche-noah-sealth-of-seattle-seattle</t>
+  </si>
+  <si>
+    <t>Caregiver Social Worker</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b76ee4734fdb467d8e6919d55d50ac07-caregiver-social-worker-greenwich-house-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Case Management Supervisor</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3612a82d60a406e961000f89a6ace1a-case-management-supervisor-greenwich-house-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Certified Recovery Peer Advocate</t>
+  </si>
+  <si>
+    <t>The Lesbian, Gay, Bisexual &amp; Transgender Community Center</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae9fd0480f8e48e08d68b06f4da97f8d-certified-recovery-peer-advocate-the-lesbian-gay-bisexual-transgender-community-center-new-york</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Carpenter's Shelter</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/06d0b37a386049abbd28ec53e1fcc9a4-chief-executive-officer-carpenters-shelter-alexandria</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f1b2f7ef8674ee19b8e277bb3160c0b-chief-financial-officer-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Civic Science Fellow (9611C), Center for the Science of Psychedelics #88430</t>
+  </si>
+  <si>
+    <t>University of California, Berkeley</t>
+  </si>
+  <si>
+    <t>Berkeley, CA</t>
+  </si>
+  <si>
+    <t>USD 78505.39 - 83281.24/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1b0c8ab1ba3d428da918bcc238c6d3df-civic-science-fellow-9611c-center-for-the-science-of-psychedelics-88430-university-of-california-berkeley-berkeley</t>
+  </si>
+  <si>
+    <t>Clothing Distribution Coordinator II</t>
+  </si>
+  <si>
+    <t>Bread for the City</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 24.04 - 24.04/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8680d9765f945b0b76a8539b5e96005-clothing-distribution-coordinator-ii-bread-for-the-city-washington</t>
+  </si>
+  <si>
+    <t>Cohort Programs Manager</t>
+  </si>
+  <si>
+    <t>UpStart</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd0e6b4988f14fc6ad7a5886de02a355-cohort-programs-manager-upstart-oakland</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>Neighbors Together</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37dbb3314f1c47e1863e5cbcb3846805-community-organizer-neighbors-together-kings-county</t>
+  </si>
+  <si>
+    <t>Coordinator of Public Advancement</t>
+  </si>
+  <si>
+    <t>Food Allergy Research &amp; Education (FARE)</t>
+  </si>
+  <si>
+    <t>Tysons, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0335a14333b0476cbcd4212807aeac43-coordinator-of-public-advancement-food-allergy-research-education-fare-tysons</t>
+  </si>
+  <si>
+    <t>Demand Planning Analyst</t>
+  </si>
+  <si>
+    <t>Patagonia</t>
+  </si>
+  <si>
+    <t>Acassuso, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/023ea230b3574c66ac669953df705fd3-demand-planning-analyst-patagonia-acassuso</t>
+  </si>
+  <si>
+    <t>Deputy Director of Development Major Gifts and Communications</t>
+  </si>
+  <si>
+    <t>Signature Theatre</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebfe5f074e2e47ad9fa0f223c82315ca-deputy-director-of-development-major-gifts-and-communications-signature-theatre-arlington</t>
+  </si>
+  <si>
+    <t>Deputy Director of Program Operations</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e27ab62b5cbb4b1e8eec60103f2379db-deputy-director-of-program-operations-hera-washington</t>
+  </si>
+  <si>
+    <t>Deputy Director, Unmoderated News</t>
+  </si>
+  <si>
+    <t>Third Way</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d869a3acdc204679aa5cffca6645f327-deputy-director-unmoderated-news-third-way-washington</t>
+  </si>
+  <si>
+    <t>Deputy Editor</t>
+  </si>
+  <si>
+    <t>Street Sense Media</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1edd2ba75f5e4b459ddf93da6418b07b-deputy-editor-street-sense-media-washington</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef1cfdaffb574f9d82e58e525dedc7be-development-communications-manager-northwest-community-bail-fund-seattle</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Breakthrough T1D (formerly known as JDRF)</t>
+  </si>
+  <si>
+    <t>Winter Park, Florida</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2f1859d2b6f491cba3e6a64cedb7b75-development-coordinator-breakthrough-t1d-formerly-known-as-jdrf-winter-park</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Welcome Center</t>
+  </si>
+  <si>
+    <t>Aurora, Colorado</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/385d4ddff93742499b1858eb9ef311c1-development-manager-rocky-mountain-welcome-center-aurora</t>
+  </si>
+  <si>
+    <t>Development Operations Coordinator</t>
+  </si>
+  <si>
+    <t>New York Common Pantry</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a0042de17a64d99a9da9d7e180c94ab-development-operations-coordinator-new-york-common-pantry-new-york</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Pace Women's Justice Center</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 98000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60720f6be2f744199465acb3fdef37a6-director-of-finance-pace-womens-justice-center-white-plains</t>
+  </si>
+  <si>
+    <t>Director of Learning, Monitoring &amp; Evaluation</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6927f2c246894ba2bb5b1b12a1b38bd7-director-of-learning-monitoring-evaluation-hera-washington</t>
+  </si>
+  <si>
+    <t>Director, Policy &amp; Advocacy, Breakwater</t>
+  </si>
+  <si>
+    <t>The Rockefeller Foundation</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Economic Development, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a96310c1c6754f5294497e8d862260f2-director-policy-advocacy-breakwater-the-rockefeller-foundation-washington</t>
+  </si>
+  <si>
+    <t>Especialista de Administración de Personal &amp; Payroll - Eventual</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5c8c552798944a68ceaab708a22dc81-especialista-de-administracion-de-personal-payroll-eventual-medicos-sin-fronteras-lat-buenos-aires</t>
+  </si>
+  <si>
+    <t>Finance and Operations Associate</t>
+  </si>
+  <si>
+    <t>Michigan Historic Preservation Network</t>
+  </si>
+  <si>
+    <t>Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/829a0535a92b4dc0ad798b76ea48bad4-finance-and-operations-associate-michigan-historic-preservation-network-lansing</t>
+  </si>
+  <si>
+    <t>Financial Wellness Program Manager</t>
+  </si>
+  <si>
+    <t>Homestretch</t>
+  </si>
+  <si>
+    <t>Falls Church, Virginia</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d03ce7218f84e05a6d8c511aa5b3df9-financial-wellness-program-manager-homestretch-falls-church</t>
+  </si>
+  <si>
+    <t>Full-time Program Director</t>
+  </si>
+  <si>
+    <t>Columbia County Community Healthcare Consortium, Inc.</t>
+  </si>
+  <si>
+    <t>Hudson, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80efd90e02964724b313f8372f95a8ad-full-time-program-director-columbia-county-community-healthcare-consortium-inc-hudson</t>
+  </si>
+  <si>
+    <t>Geriatric Case Manager</t>
+  </si>
+  <si>
+    <t>USD 66500.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2da612b1798f4179aa294b9db460059c-geriatric-case-manager-greenwich-house-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Grant Writer Consultant</t>
+  </si>
+  <si>
+    <t>GreenRoots, Inc.</t>
+  </si>
+  <si>
+    <t>Chelsea, Massachusetts</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 65.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2eb9e61a391c47eabe2c1b6f9e1de180-grant-writer-consultant-greenroots-inc-chelsea</t>
+  </si>
+  <si>
+    <t>Group Leader [Bronx]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5387de6546ee4598bf18c8f834f98c02-group-leader-bronx-replications-inc-bronx</t>
+  </si>
+  <si>
+    <t>Group Leader [Brooklyn]</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4b59900b36c49c1981a8734d2507965-group-leader-brooklyn-replications-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Large Scale Partnerships Manager (Wonder Grant)</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>USD 5000.00 - 5000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/180ed5a6188a4a3dbf66502f9c682931-large-scale-partnerships-manager-wonder-grant-rescuing-leftover-cuisine-new-york</t>
+  </si>
+  <si>
+    <t>Legal Case Manager (Bilingual)</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2a8d206aed24e6692de6c825b4df779-legal-case-manager-bilingual-a-safe-place-waukegan</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Riverdale Park, Maryland</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a366083973f494fb206ec48cd10da09-major-gifts-officer-central-union-mission-riverdale-park</t>
+  </si>
+  <si>
+    <t>Manager, Operations, Breakwater</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4db1480a200d4c7c8ea6021d1c09239e-manager-operations-breakwater-the-rockefeller-foundation-washington</t>
+  </si>
+  <si>
+    <t>Manager/Senior Manager, Generosity and Strategic Partnerships</t>
+  </si>
+  <si>
+    <t>Hope for New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78cb0a615fcf471ab16aad6b14a792e8-managersenior-manager-generosity-and-strategic-partnerships-hope-for-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Managing Director, Policy, Breakwater</t>
+  </si>
+  <si>
+    <t>USD 240000.00 - 305000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Philanthropy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96fc8f27c3d848ce9d03a1f926a26d09-managing-director-policy-breakwater-the-rockefeller-foundation-washington</t>
+  </si>
+  <si>
+    <t>Nonprofit Finance Associate</t>
+  </si>
+  <si>
+    <t>Finance Friend</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/0597ebd7365e41e289e6e68ca04203a7-nonprofit-finance-associate-finance-friend-nyack</t>
+  </si>
+  <si>
+    <t>Nonprofit Finance Director</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/8e129ec9069342d391db4f5b8bf4c568-nonprofit-finance-director-finance-friend-nyack</t>
+  </si>
+  <si>
+    <t>Nonprofit Finance Manager</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6021b76395c94cccaa7615db47034ed4-nonprofit-finance-manager-finance-friend-nyack</t>
+  </si>
+  <si>
+    <t>Nonprofit Finance Manager (Theatre Division)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/bc617512ef214acbb35e8c3a18fd05b3-nonprofit-finance-manager-theatre-division-finance-friend-nyack</t>
+  </si>
+  <si>
+    <t>Operations &amp; Executive Support Coordinator</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2057f40841044591838b26fca1851635-operations-executive-support-coordinator-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Operations and Membership Manager</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Job Workplace, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bf2ba8acbf194808ae9e05d1250d133c-operations-and-membership-manager-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>Center for Constitutional Rights</t>
+  </si>
+  <si>
+    <t>USD 42533.00 - 55425.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35a4beea8ae54a4f980750c2212394fc-operations-associate-center-for-constitutional-rights-new-york</t>
+  </si>
+  <si>
+    <t>Organizer in Training (Paid)</t>
+  </si>
+  <si>
+    <t>C4C Oakland Action, Inc.</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9eb273fdd060468a82bb5b8fcf4d415b-organizer-in-training-paid-c4c-oakland-action-inc-oakland</t>
+  </si>
+  <si>
+    <t>Outcome Team Manager</t>
+  </si>
+  <si>
+    <t>FRIENDS OF OAKLAND ANIMAL SERVICES</t>
+  </si>
+  <si>
+    <t>Animals, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fdc14a3243b495ca8871d4b918ce6f4-outcome-team-manager-friends-of-oakland-animal-services-oakland</t>
+  </si>
+  <si>
+    <t>Portfolio Associate</t>
+  </si>
+  <si>
+    <t>Community Economic Development Assistance Corp. (CEDAC)</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 60080.00 - 63835.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28c65e69bc1b4a74845f55a9eb78d3f4-portfolio-associate-community-economic-development-assistance-corp-cedac-boston</t>
+  </si>
+  <si>
+    <t>Princeton University - Eviction Lab</t>
+  </si>
+  <si>
+    <t>Princeton, New Jersey</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf1eaebaef4a45a08cf6c547acb8b74f-postdoctoral-research-associate-princeton-university-eviction-lab-princeton</t>
+  </si>
+  <si>
+    <t>Preschool Assistant Teacher - Temporary Sub</t>
+  </si>
+  <si>
+    <t>Seattle PlayGarden</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b71365045604d0a89fa0fa6c54afff5-preschool-assistant-teacher-temporary-sub-seattle-playgarden-seattle</t>
+  </si>
+  <si>
+    <t>President &amp; CEO</t>
+  </si>
+  <si>
+    <t>Mid-Ohio Food Collective</t>
+  </si>
+  <si>
+    <t>Grove City, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f0700d7a44914706a556247f11ca5dfc-president-ceo-mid-ohio-food-collective-grove-city</t>
+  </si>
+  <si>
+    <t>PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Internationals Network for Public Schools</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/753e1e4383154c0c948c5d49fb77f1e3-program-associate-internationals-network-for-public-schools-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate, Strategic Initiatives</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>USD 58400.00 - 80300.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64f6af9ba18442198ac22d38d1b8cac7-program-associate-strategic-initiatives-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>USD 60800.00 - 83600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/318cd3c45b974d82907033d26ebf3103-program-associate-strategic-initiatives-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>Program Support Coordinator</t>
+  </si>
+  <si>
+    <t>California IT in Education (CITE)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1970d5530c7426e90a8cb75b8dd2eb1-program-support-coordinator-california-it-in-education-cite-sacramento</t>
+  </si>
+  <si>
+    <t>Senior Administrative Coordinator, Programs &amp; Services</t>
+  </si>
+  <si>
+    <t>NAMI (National Alliance on Mental Illness)</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1b5a725577245cd8f9a53a38e0db34c-senior-administrative-coordinator-programs-services-nami-national-alliance-on-mental-illness-arlington</t>
+  </si>
+  <si>
+    <t>Senior Fundraising Copywriter</t>
+  </si>
+  <si>
+    <t>The Avalon Consulting Group, LLC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/dee1212a08b4464caf420bc5dc7f2733-senior-fundraising-copywriter-the-avalon-consulting-group-llc-annapolis</t>
+  </si>
+  <si>
+    <t>Senior Manager, Individual Giving</t>
+  </si>
+  <si>
+    <t>City Year Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0954a3c680d4ad6b7cbf3b72d3091cd-senior-manager-individual-giving-city-year-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Senior Operations Manager</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Transparency Oversight, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2b08f36954a4173b7b17c2d2574677d-senior-operations-manager-california-it-in-education-cite-sacramento</t>
+  </si>
+  <si>
+    <t>Senior Project Manager or Project Manager</t>
+  </si>
+  <si>
+    <t>The Planning Office for Urban Affairs (POUA, the Planning Office)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67ee4b66af964e609a3cfe91229ad2c2-senior-project-manager-or-project-manager-the-planning-office-for-urban-affairs-poua-the-planning-office-boston</t>
+  </si>
+  <si>
+    <t>Social Work Lead / Manager</t>
+  </si>
+  <si>
+    <t>VAST BC - Vancouver Association for Survivors of Torture</t>
+  </si>
+  <si>
+    <t>Surrey, British Columbia, CA</t>
+  </si>
+  <si>
+    <t>CAD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/104642f06bbe460eba09d077c919ec07-social-work-lead-manager-vast-bc-vancouver-association-for-survivors-of-torture-surrey</t>
+  </si>
+  <si>
+    <t>Special Assistant to the CEO, Breakwater</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 123000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97605e8ef1004c0889f0ddbee7d0b6cb-special-assistant-to-the-ceo-breakwater-the-rockefeller-foundation-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Vermont Afghan Alliance Incorporated</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d03d1cbe245426aa228ed302a3d0243-staff-attorney-vermont-afghan-alliance-incorporated-burlington</t>
+  </si>
+  <si>
+    <t>Council on American-Islamic Relations, New York Chapter (CAIR-NY)</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5bb6d34f27a4f2191082f35d42bc474-staff-attorney-council-on-american-islamic-relations-new-york-chapter-cair-ny-new-york</t>
+  </si>
+  <si>
+    <t>Cesar Chavez Foundation</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/210500305da144afb125b3dd6e88fb5d-staff-attorney-cesar-chavez-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Strategic Finance Director</t>
+  </si>
+  <si>
+    <t>DonorsChoose</t>
+  </si>
+  <si>
+    <t>USD 109180.00 - 142000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a282262a87b4239aab1599551f47ed4-strategic-finance-director-donorschoose-new-york</t>
+  </si>
+  <si>
+    <t>Vice President, Mobilization and Generosity</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5852e4b8cc2744b682a1442c255c748b-vice-president-mobilization-and-generosity-hope-for-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Wellbeing Navigator</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 75507.00 - 83897.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1afad37947924626833a7bfe79c1ccf0-wellbeing-navigator-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Youth Employment Specialist</t>
+  </si>
+  <si>
+    <t>Bridges From School to Work Inc.</t>
+  </si>
+  <si>
+    <t>West Palm Beach, Florida</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb2fcf36506a495289799dba843aa2ca-youth-employment-specialist-bridges-from-school-to-work-inc-west-palm-beach</t>
+  </si>
+  <si>
+    <t>Youth Programs Organizer</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e1b09e554164141bd0fb4e99e50db6c-youth-programs-organizer-greenroots-inc-chelsea</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1911,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1937,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2319,1138 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" t="s">
+        <v>166</v>
+      </c>
+      <c r="D32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>179</v>
+      </c>
+      <c r="F35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>149</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" t="s">
+        <v>191</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>200</v>
+      </c>
+      <c r="F40" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>202</v>
+      </c>
+      <c r="B41" t="s">
+        <v>195</v>
+      </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>208</v>
+      </c>
+      <c r="B43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" t="s">
+        <v>212</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>215</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>219</v>
+      </c>
+      <c r="C45" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" t="s">
+        <v>229</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" t="s">
+        <v>231</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="s">
+        <v>234</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3506,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3545,1954 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" t="s">
+        <v>259</v>
+      </c>
+      <c r="F5" t="s">
+        <v>260</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10" t="s">
+        <v>253</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F11" t="s">
+        <v>290</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" t="s">
+        <v>296</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" t="s">
+        <v>302</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" t="s">
+        <v>307</v>
+      </c>
+      <c r="F14" t="s">
+        <v>308</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" t="s">
+        <v>278</v>
+      </c>
+      <c r="D15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" t="s">
+        <v>311</v>
+      </c>
+      <c r="F15" t="s">
+        <v>280</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>313</v>
+      </c>
+      <c r="B16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C17" t="s">
+        <v>318</v>
+      </c>
+      <c r="D17" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" t="s">
+        <v>320</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D18" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F18" t="s">
+        <v>325</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C19" t="s">
+        <v>329</v>
+      </c>
+      <c r="D19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" t="s">
+        <v>330</v>
+      </c>
+      <c r="F19" t="s">
+        <v>331</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" t="s">
+        <v>335</v>
+      </c>
+      <c r="D20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" t="s">
+        <v>336</v>
+      </c>
+      <c r="F20" t="s">
+        <v>253</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" t="s">
+        <v>339</v>
+      </c>
+      <c r="C21" t="s">
+        <v>340</v>
+      </c>
+      <c r="D21" t="s">
+        <v>341</v>
+      </c>
+      <c r="E21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F21" t="s">
+        <v>343</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>345</v>
+      </c>
+      <c r="B22" t="s">
+        <v>346</v>
+      </c>
+      <c r="C22" t="s">
+        <v>347</v>
+      </c>
+      <c r="D22" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" t="s">
+        <v>348</v>
+      </c>
+      <c r="F22" t="s">
+        <v>349</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B23" t="s">
+        <v>352</v>
+      </c>
+      <c r="C23" t="s">
+        <v>278</v>
+      </c>
+      <c r="D23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" t="s">
+        <v>353</v>
+      </c>
+      <c r="F23" t="s">
+        <v>354</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>356</v>
+      </c>
+      <c r="B24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C24" t="s">
+        <v>358</v>
+      </c>
+      <c r="D24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" t="s">
+        <v>252</v>
+      </c>
+      <c r="F24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>360</v>
+      </c>
+      <c r="B25" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F25" t="s">
+        <v>253</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>364</v>
+      </c>
+      <c r="B26" t="s">
+        <v>365</v>
+      </c>
+      <c r="C26" t="s">
+        <v>366</v>
+      </c>
+      <c r="D26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E26" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" t="s">
+        <v>368</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" t="s">
+        <v>371</v>
+      </c>
+      <c r="C27" t="s">
+        <v>347</v>
+      </c>
+      <c r="D27" t="s">
+        <v>239</v>
+      </c>
+      <c r="E27" t="s">
+        <v>372</v>
+      </c>
+      <c r="F27" t="s">
+        <v>373</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>375</v>
+      </c>
+      <c r="B28" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" t="s">
+        <v>340</v>
+      </c>
+      <c r="D28" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" t="s">
+        <v>377</v>
+      </c>
+      <c r="F28" t="s">
+        <v>378</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>380</v>
+      </c>
+      <c r="B29" t="s">
+        <v>381</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" t="s">
+        <v>382</v>
+      </c>
+      <c r="F29" t="s">
+        <v>383</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30" t="s">
+        <v>251</v>
+      </c>
+      <c r="D30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E30" t="s">
+        <v>252</v>
+      </c>
+      <c r="F30" t="s">
+        <v>253</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>387</v>
+      </c>
+      <c r="B31" t="s">
+        <v>388</v>
+      </c>
+      <c r="C31" t="s">
+        <v>389</v>
+      </c>
+      <c r="D31" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" t="s">
+        <v>390</v>
+      </c>
+      <c r="F31" t="s">
+        <v>391</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>393</v>
+      </c>
+      <c r="C32" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E32" t="s">
+        <v>395</v>
+      </c>
+      <c r="F32" t="s">
+        <v>396</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>398</v>
+      </c>
+      <c r="B33" t="s">
+        <v>399</v>
+      </c>
+      <c r="C33" t="s">
+        <v>269</v>
+      </c>
+      <c r="D33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" t="s">
+        <v>400</v>
+      </c>
+      <c r="F33" t="s">
+        <v>253</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>402</v>
+      </c>
+      <c r="B34" t="s">
+        <v>403</v>
+      </c>
+      <c r="C34" t="s">
+        <v>404</v>
+      </c>
+      <c r="D34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" t="s">
+        <v>405</v>
+      </c>
+      <c r="F34" t="s">
+        <v>406</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>408</v>
+      </c>
+      <c r="B35" t="s">
+        <v>371</v>
+      </c>
+      <c r="C35" t="s">
+        <v>347</v>
+      </c>
+      <c r="D35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" t="s">
+        <v>409</v>
+      </c>
+      <c r="F35" t="s">
+        <v>373</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>411</v>
+      </c>
+      <c r="B36" t="s">
+        <v>412</v>
+      </c>
+      <c r="C36" t="s">
+        <v>340</v>
+      </c>
+      <c r="D36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" t="s">
+        <v>413</v>
+      </c>
+      <c r="F36" t="s">
+        <v>414</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>416</v>
+      </c>
+      <c r="B37" t="s">
+        <v>417</v>
+      </c>
+      <c r="C37" t="s">
+        <v>418</v>
+      </c>
+      <c r="D37" t="s">
+        <v>341</v>
+      </c>
+      <c r="E37" t="s">
+        <v>253</v>
+      </c>
+      <c r="F37" t="s">
+        <v>419</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>421</v>
+      </c>
+      <c r="B38" t="s">
+        <v>422</v>
+      </c>
+      <c r="C38" t="s">
+        <v>423</v>
+      </c>
+      <c r="D38" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" t="s">
+        <v>424</v>
+      </c>
+      <c r="F38" t="s">
+        <v>425</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>427</v>
+      </c>
+      <c r="B39" t="s">
+        <v>428</v>
+      </c>
+      <c r="C39" t="s">
+        <v>429</v>
+      </c>
+      <c r="D39" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" t="s">
+        <v>252</v>
+      </c>
+      <c r="F39" t="s">
+        <v>430</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>432</v>
+      </c>
+      <c r="B40" t="s">
+        <v>433</v>
+      </c>
+      <c r="C40" t="s">
+        <v>434</v>
+      </c>
+      <c r="D40" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" t="s">
+        <v>435</v>
+      </c>
+      <c r="F40" t="s">
+        <v>436</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>438</v>
+      </c>
+      <c r="B41" t="s">
+        <v>277</v>
+      </c>
+      <c r="C41" t="s">
+        <v>278</v>
+      </c>
+      <c r="D41" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" t="s">
+        <v>439</v>
+      </c>
+      <c r="F41" t="s">
+        <v>440</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>442</v>
+      </c>
+      <c r="B42" t="s">
+        <v>443</v>
+      </c>
+      <c r="C42" t="s">
+        <v>444</v>
+      </c>
+      <c r="D42" t="s">
+        <v>445</v>
+      </c>
+      <c r="E42" t="s">
+        <v>446</v>
+      </c>
+      <c r="F42" t="s">
+        <v>447</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>449</v>
+      </c>
+      <c r="B43" t="s">
+        <v>450</v>
+      </c>
+      <c r="C43" t="s">
+        <v>451</v>
+      </c>
+      <c r="D43" t="s">
+        <v>258</v>
+      </c>
+      <c r="E43" t="s">
+        <v>452</v>
+      </c>
+      <c r="F43" t="s">
+        <v>453</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>455</v>
+      </c>
+      <c r="B44" t="s">
+        <v>450</v>
+      </c>
+      <c r="C44" t="s">
+        <v>456</v>
+      </c>
+      <c r="D44" t="s">
+        <v>258</v>
+      </c>
+      <c r="E44" t="s">
+        <v>452</v>
+      </c>
+      <c r="F44" t="s">
+        <v>453</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>458</v>
+      </c>
+      <c r="B45" t="s">
+        <v>459</v>
+      </c>
+      <c r="C45" t="s">
+        <v>269</v>
+      </c>
+      <c r="D45" t="s">
+        <v>445</v>
+      </c>
+      <c r="E45" t="s">
+        <v>460</v>
+      </c>
+      <c r="F45" t="s">
+        <v>461</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>463</v>
+      </c>
+      <c r="B46" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" t="s">
+        <v>294</v>
+      </c>
+      <c r="D46" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46" t="s">
+        <v>464</v>
+      </c>
+      <c r="F46" t="s">
+        <v>296</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>466</v>
+      </c>
+      <c r="B47" t="s">
+        <v>467</v>
+      </c>
+      <c r="C47" t="s">
+        <v>468</v>
+      </c>
+      <c r="D47" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" t="s">
+        <v>469</v>
+      </c>
+      <c r="F47" t="s">
+        <v>470</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>472</v>
+      </c>
+      <c r="B48" t="s">
+        <v>412</v>
+      </c>
+      <c r="C48" t="s">
+        <v>340</v>
+      </c>
+      <c r="D48" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" t="s">
+        <v>473</v>
+      </c>
+      <c r="F48" t="s">
+        <v>474</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>476</v>
+      </c>
+      <c r="B49" t="s">
+        <v>477</v>
+      </c>
+      <c r="C49" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" t="s">
+        <v>239</v>
+      </c>
+      <c r="E49" t="s">
+        <v>478</v>
+      </c>
+      <c r="F49" t="s">
+        <v>479</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>481</v>
+      </c>
+      <c r="B50" t="s">
+        <v>412</v>
+      </c>
+      <c r="C50" t="s">
+        <v>340</v>
+      </c>
+      <c r="D50" t="s">
+        <v>239</v>
+      </c>
+      <c r="E50" t="s">
+        <v>482</v>
+      </c>
+      <c r="F50" t="s">
+        <v>483</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>485</v>
+      </c>
+      <c r="B51" t="s">
+        <v>486</v>
+      </c>
+      <c r="C51" t="s">
+        <v>347</v>
+      </c>
+      <c r="D51" t="s">
+        <v>258</v>
+      </c>
+      <c r="E51" t="s">
+        <v>487</v>
+      </c>
+      <c r="F51" t="s">
+        <v>488</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>490</v>
+      </c>
+      <c r="B52" t="s">
+        <v>486</v>
+      </c>
+      <c r="C52" t="s">
+        <v>347</v>
+      </c>
+      <c r="D52" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" t="s">
+        <v>491</v>
+      </c>
+      <c r="F52" t="s">
+        <v>488</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>493</v>
+      </c>
+      <c r="B53" t="s">
+        <v>486</v>
+      </c>
+      <c r="C53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D53" t="s">
+        <v>239</v>
+      </c>
+      <c r="E53" t="s">
+        <v>494</v>
+      </c>
+      <c r="F53" t="s">
+        <v>488</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>496</v>
+      </c>
+      <c r="B54" t="s">
+        <v>486</v>
+      </c>
+      <c r="C54" t="s">
+        <v>347</v>
+      </c>
+      <c r="D54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" t="s">
+        <v>494</v>
+      </c>
+      <c r="F54" t="s">
+        <v>488</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B55" t="s">
+        <v>499</v>
+      </c>
+      <c r="C55" t="s">
+        <v>340</v>
+      </c>
+      <c r="D55" t="s">
+        <v>341</v>
+      </c>
+      <c r="E55" t="s">
+        <v>487</v>
+      </c>
+      <c r="F55" t="s">
+        <v>500</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>502</v>
+      </c>
+      <c r="B56" t="s">
+        <v>499</v>
+      </c>
+      <c r="C56" t="s">
+        <v>340</v>
+      </c>
+      <c r="D56" t="s">
+        <v>239</v>
+      </c>
+      <c r="E56" t="s">
+        <v>503</v>
+      </c>
+      <c r="F56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>506</v>
+      </c>
+      <c r="B57" t="s">
+        <v>507</v>
+      </c>
+      <c r="C57" t="s">
+        <v>269</v>
+      </c>
+      <c r="D57" t="s">
+        <v>258</v>
+      </c>
+      <c r="E57" t="s">
+        <v>508</v>
+      </c>
+      <c r="F57" t="s">
+        <v>509</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>511</v>
+      </c>
+      <c r="B58" t="s">
+        <v>512</v>
+      </c>
+      <c r="C58" t="s">
+        <v>513</v>
+      </c>
+      <c r="D58" t="s">
+        <v>341</v>
+      </c>
+      <c r="E58" t="s">
+        <v>514</v>
+      </c>
+      <c r="F58" t="s">
+        <v>515</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>517</v>
+      </c>
+      <c r="B59" t="s">
+        <v>518</v>
+      </c>
+      <c r="C59" t="s">
+        <v>513</v>
+      </c>
+      <c r="D59" t="s">
+        <v>239</v>
+      </c>
+      <c r="E59" t="s">
+        <v>478</v>
+      </c>
+      <c r="F59" t="s">
+        <v>519</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>521</v>
+      </c>
+      <c r="B60" t="s">
+        <v>522</v>
+      </c>
+      <c r="C60" t="s">
+        <v>523</v>
+      </c>
+      <c r="D60" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" t="s">
+        <v>524</v>
+      </c>
+      <c r="F60" t="s">
+        <v>525</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" t="s">
+        <v>527</v>
+      </c>
+      <c r="C61" t="s">
+        <v>528</v>
+      </c>
+      <c r="D61" t="s">
+        <v>239</v>
+      </c>
+      <c r="E61" t="s">
+        <v>253</v>
+      </c>
+      <c r="F61" t="s">
+        <v>529</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>531</v>
+      </c>
+      <c r="B62" t="s">
+        <v>532</v>
+      </c>
+      <c r="C62" t="s">
+        <v>306</v>
+      </c>
+      <c r="D62" t="s">
+        <v>533</v>
+      </c>
+      <c r="E62" t="s">
+        <v>534</v>
+      </c>
+      <c r="F62" t="s">
+        <v>535</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>537</v>
+      </c>
+      <c r="B63" t="s">
+        <v>538</v>
+      </c>
+      <c r="C63" t="s">
+        <v>539</v>
+      </c>
+      <c r="D63" t="s">
+        <v>239</v>
+      </c>
+      <c r="E63" t="s">
+        <v>253</v>
+      </c>
+      <c r="F63" t="s">
+        <v>253</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>541</v>
+      </c>
+      <c r="B64" t="s">
+        <v>542</v>
+      </c>
+      <c r="C64" t="s">
+        <v>269</v>
+      </c>
+      <c r="D64" t="s">
+        <v>239</v>
+      </c>
+      <c r="E64" t="s">
+        <v>543</v>
+      </c>
+      <c r="F64" t="s">
+        <v>544</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>546</v>
+      </c>
+      <c r="B65" t="s">
+        <v>547</v>
+      </c>
+      <c r="C65" t="s">
+        <v>340</v>
+      </c>
+      <c r="D65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E65" t="s">
+        <v>548</v>
+      </c>
+      <c r="F65" t="s">
+        <v>549</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>546</v>
+      </c>
+      <c r="B66" t="s">
+        <v>547</v>
+      </c>
+      <c r="C66" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" t="s">
+        <v>239</v>
+      </c>
+      <c r="E66" t="s">
+        <v>551</v>
+      </c>
+      <c r="F66" t="s">
+        <v>549</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>553</v>
+      </c>
+      <c r="B67" t="s">
+        <v>554</v>
+      </c>
+      <c r="C67" t="s">
+        <v>555</v>
+      </c>
+      <c r="D67" t="s">
+        <v>239</v>
+      </c>
+      <c r="E67" t="s">
+        <v>503</v>
+      </c>
+      <c r="F67" t="s">
+        <v>556</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>558</v>
+      </c>
+      <c r="B68" t="s">
+        <v>559</v>
+      </c>
+      <c r="C68" t="s">
+        <v>347</v>
+      </c>
+      <c r="D68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" t="s">
+        <v>560</v>
+      </c>
+      <c r="F68" t="s">
+        <v>561</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>563</v>
+      </c>
+      <c r="B69" t="s">
+        <v>564</v>
+      </c>
+      <c r="C69" t="s">
+        <v>347</v>
+      </c>
+      <c r="D69" t="s">
+        <v>239</v>
+      </c>
+      <c r="E69" t="s">
+        <v>469</v>
+      </c>
+      <c r="F69" t="s">
+        <v>253</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>566</v>
+      </c>
+      <c r="B70" t="s">
+        <v>567</v>
+      </c>
+      <c r="C70" t="s">
+        <v>568</v>
+      </c>
+      <c r="D70" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" t="s">
+        <v>569</v>
+      </c>
+      <c r="F70" t="s">
+        <v>320</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>571</v>
+      </c>
+      <c r="B71" t="s">
+        <v>554</v>
+      </c>
+      <c r="C71" t="s">
+        <v>555</v>
+      </c>
+      <c r="D71" t="s">
+        <v>239</v>
+      </c>
+      <c r="E71" t="s">
+        <v>572</v>
+      </c>
+      <c r="F71" t="s">
+        <v>573</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>575</v>
+      </c>
+      <c r="B72" t="s">
+        <v>576</v>
+      </c>
+      <c r="C72" t="s">
+        <v>329</v>
+      </c>
+      <c r="D72" t="s">
+        <v>239</v>
+      </c>
+      <c r="E72" t="s">
+        <v>577</v>
+      </c>
+      <c r="F72" t="s">
+        <v>578</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>580</v>
+      </c>
+      <c r="B73" t="s">
+        <v>581</v>
+      </c>
+      <c r="C73" t="s">
+        <v>582</v>
+      </c>
+      <c r="D73" t="s">
+        <v>239</v>
+      </c>
+      <c r="E73" t="s">
+        <v>583</v>
+      </c>
+      <c r="F73" t="s">
+        <v>584</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>586</v>
+      </c>
+      <c r="B74" t="s">
+        <v>412</v>
+      </c>
+      <c r="C74" t="s">
+        <v>340</v>
+      </c>
+      <c r="D74" t="s">
+        <v>239</v>
+      </c>
+      <c r="E74" t="s">
+        <v>587</v>
+      </c>
+      <c r="F74" t="s">
+        <v>474</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>589</v>
+      </c>
+      <c r="B75" t="s">
+        <v>590</v>
+      </c>
+      <c r="C75" t="s">
+        <v>591</v>
+      </c>
+      <c r="D75" t="s">
+        <v>341</v>
+      </c>
+      <c r="E75" t="s">
+        <v>592</v>
+      </c>
+      <c r="F75" t="s">
+        <v>593</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>589</v>
+      </c>
+      <c r="B76" t="s">
+        <v>595</v>
+      </c>
+      <c r="C76" t="s">
+        <v>269</v>
+      </c>
+      <c r="D76" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" t="s">
+        <v>289</v>
+      </c>
+      <c r="F76" t="s">
+        <v>596</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>589</v>
+      </c>
+      <c r="B77" t="s">
+        <v>598</v>
+      </c>
+      <c r="C77" t="s">
+        <v>599</v>
+      </c>
+      <c r="D77" t="s">
+        <v>239</v>
+      </c>
+      <c r="E77" t="s">
+        <v>600</v>
+      </c>
+      <c r="F77" t="s">
+        <v>601</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>603</v>
+      </c>
+      <c r="B78" t="s">
+        <v>604</v>
+      </c>
+      <c r="C78" t="s">
+        <v>347</v>
+      </c>
+      <c r="D78" t="s">
+        <v>239</v>
+      </c>
+      <c r="E78" t="s">
+        <v>605</v>
+      </c>
+      <c r="F78" t="s">
+        <v>606</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>608</v>
+      </c>
+      <c r="B79" t="s">
+        <v>477</v>
+      </c>
+      <c r="C79" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" t="s">
+        <v>239</v>
+      </c>
+      <c r="E79" t="s">
+        <v>609</v>
+      </c>
+      <c r="F79" t="s">
+        <v>610</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>612</v>
+      </c>
+      <c r="B80" t="s">
+        <v>613</v>
+      </c>
+      <c r="C80" t="s">
+        <v>614</v>
+      </c>
+      <c r="D80" t="s">
+        <v>239</v>
+      </c>
+      <c r="E80" t="s">
+        <v>615</v>
+      </c>
+      <c r="F80" t="s">
+        <v>616</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>618</v>
+      </c>
+      <c r="B81" t="s">
+        <v>619</v>
+      </c>
+      <c r="C81" t="s">
+        <v>620</v>
+      </c>
+      <c r="D81" t="s">
+        <v>239</v>
+      </c>
+      <c r="E81" t="s">
+        <v>503</v>
+      </c>
+      <c r="F81" t="s">
+        <v>621</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>623</v>
+      </c>
+      <c r="B82" t="s">
+        <v>443</v>
+      </c>
+      <c r="C82" t="s">
+        <v>444</v>
+      </c>
+      <c r="D82" t="s">
+        <v>239</v>
+      </c>
+      <c r="E82" t="s">
+        <v>624</v>
+      </c>
+      <c r="F82" t="s">
+        <v>625</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-16.xlsx
+++ b/docs/xlsx/jobs-2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="901">
   <si>
     <t>Title</t>
   </si>
@@ -724,6 +724,27 @@
     <t>https://www.conservationjobboard.com/job-listing-youth-education-specialist-minneapolis-minnesota/3172449921</t>
   </si>
   <si>
+    <t>Account Manager | Santa Fe, New Mexico</t>
+  </si>
+  <si>
+    <t>CheckBox Pro</t>
+  </si>
+  <si>
+    <t>Santa Fe, New Mexico</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/bb466b1343fa4554ba0b8c21b0ebf93c-account-manager-santa-fe-new-mexico-checkbox-pro-santa-fe</t>
+  </si>
+  <si>
     <t>Administrative Assistant</t>
   </si>
   <si>
@@ -745,6 +766,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/6f598568af6c4a8681f911515fe34098-administrative-assistant-de-novo-center-for-justice-and-healing-cambridge</t>
   </si>
   <si>
+    <t>Administrative Assistant/English-Spanish Translator</t>
+  </si>
+  <si>
+    <t>AIDS Center of Queens County, Inc. - ACQC</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 17.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fae9fbd8d3fb416b8aaa6ed1835faf80-administrative-assistantenglish-spanish-translator-aids-center-of-queens-county-inc-acqc-queens-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef323436c0994bb59f9eeeee4f29a256-administrative-assistantenglish-spanish-translator-aids-center-of-queens-county-inc-acqc-queens-county</t>
+  </si>
+  <si>
     <t>Administrative Specialist - Personnel and Human Resources</t>
   </si>
   <si>
@@ -790,9 +835,6 @@
     <t>Remote (New York)</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 30.00/hour</t>
   </si>
   <si>
@@ -802,6 +844,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/010ffb912109499d8d95709eb818d1fb-alternatives-to-violence-project-new-york-office-adminstrator-alternatives-to-violence-project-inc-ithaca</t>
   </si>
   <si>
+    <t>Alumni Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Fellowships at Auschwitz for the Study of Professional Ethics</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3411f7e9f63c4452883822d12363c029-alumni-engagement-coordinator-fellowships-at-auschwitz-for-the-study-of-professional-ethics-new-york</t>
+  </si>
+  <si>
     <t>Analista de Projetos Pleno - Vaga Exclusivamente para pessoas negras e indígenas</t>
   </si>
   <si>
@@ -817,15 +874,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/61d571006330475e9726d251e51c83d0-analista-de-projetos-pleno-vaga-exclusivamente-para-pessoas-negras-e-indigenas-instituto-brasileiro-de-defesa-do-consumidor-sao-paulo</t>
   </si>
   <si>
+    <t>Annual Giving &amp; Stewardship Program Manager</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Greater Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2007ac4481cf4b5f923f44da2bf0f672-annual-giving-stewardship-program-manager-make-a-wish-greater-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Assistant Attorney General, Consumer Frauds Bureau (3912)</t>
   </si>
   <si>
     <t>New York State Office of the Attorney General</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 91506.00 - 190643.00/year</t>
   </si>
   <si>
@@ -862,6 +931,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/87d982ceac3e4026bb634135d963f6bd-assistant-director-caregiver-program-greenwich-house-inc-kings-county</t>
   </si>
   <si>
+    <t>Assistant Director of Information Technology</t>
+  </si>
+  <si>
+    <t>National Cathedral School</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71da6f2b741747958dc60a16db1e2133-assistant-director-of-information-technology-national-cathedral-school-washington</t>
+  </si>
+  <si>
     <t>Assistant Director, Programs and Student Leadership</t>
   </si>
   <si>
@@ -877,6 +964,66 @@
     <t>https://www.idealist.org/en/job/5fbe6eadfaf4438b972d84cbbf75418e-assistant-director-programs-and-student-leadership-bentley-university-waltham</t>
   </si>
   <si>
+    <t>Assistant Teacher</t>
+  </si>
+  <si>
+    <t>Children's Learning Centers of Fairfield County</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 19.24 - 20.80/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6650838d853e4e169ad9eb98babbf7ff-assistant-teacher-childrens-learning-centers-of-fairfield-county-stamford</t>
+  </si>
+  <si>
+    <t>Associate Clinical Intake and Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>OUR HOUSE Grief Support Center</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20bccca54edb4700accd0bb0c5054c14-associate-clinical-intake-and-volunteer-coordinator-our-house-grief-support-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Associate Community Organizer</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Lakeland, Florida</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/635b95159a834229b239b470854e5e0c-associate-community-organizer-direct-action-research-training-center-lakeland</t>
+  </si>
+  <si>
+    <t>Associate Supervising Attorney</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 103936.00 - 114638.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1ace4d0e9884c24820c7d5499dede9a-associate-supervising-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
     <t>Audience Engagement Manager</t>
   </si>
   <si>
@@ -910,6 +1057,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/044f08ccb6484ad185381f8a035449a5-bilingual-paralegal-a-safe-place-waukegan</t>
   </si>
   <si>
+    <t>BILINGUALRECEPTIONIST- FULL-TIME</t>
+  </si>
+  <si>
+    <t>SPOP - Service Program for Older People, Inc.</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbf37a88fc034a509fda2e0d8ae1d905-bilingualreceptionist-full-time-spop-service-program-for-older-people-inc-new-york</t>
+  </si>
+  <si>
     <t>Billing Specialist</t>
   </si>
   <si>
@@ -928,6 +1090,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ac800d39f29b4d67868681dca6167059-billing-specialist-veterans-inc-shrewsbury</t>
   </si>
   <si>
+    <t>Business Development &amp; Monetization Manager</t>
+  </si>
+  <si>
+    <t>Aeronord Media</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 100.00 - 1000.00/month</t>
+  </si>
+  <si>
+    <t>Media, Economic Development, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72697c0358ef428786fc870b118c7381-business-development-monetization-manager-aeronord-media-seoul</t>
+  </si>
+  <si>
     <t>Care Companion to Adults with Developmental Disabilities in Intentional Community</t>
   </si>
   <si>
@@ -964,6 +1144,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/b3612a82d60a406e961000f89a6ace1a-case-management-supervisor-greenwich-house-inc-kings-county</t>
   </si>
   <si>
+    <t>Central Iowa Canvass Director</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Remote (Des Moines, Iowa)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 53300.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Consumer Protection, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7054d641f9d5438faece02df8c3ca427-central-iowa-canvass-director-food-water-watch-des-moines</t>
+  </si>
+  <si>
     <t>Certified Recovery Peer Advocate</t>
   </si>
   <si>
@@ -1030,18 +1231,27 @@
     <t>https://www.idealist.org/en/job/1b0c8ab1ba3d428da918bcc238c6d3df-civic-science-fellow-9611c-center-for-the-science-of-psychedelics-88430-university-of-california-berkeley-berkeley</t>
   </si>
   <si>
+    <t>Clinic Operations Director</t>
+  </si>
+  <si>
+    <t>Vot-ER</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/baefa0466ab94d93bd87a5fd28e7e5c0-clinic-operations-director-vot-er-boston</t>
+  </si>
+  <si>
     <t>Clothing Distribution Coordinator II</t>
   </si>
   <si>
     <t>Bread for the City</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 24.04 - 24.04/hour</t>
   </si>
   <si>
@@ -1057,9 +1267,6 @@
     <t>UpStart</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 70000.00/year</t>
   </si>
   <si>
@@ -1069,6 +1276,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/dd0e6b4988f14fc6ad7a5886de02a355-cohort-programs-manager-upstart-oakland</t>
   </si>
   <si>
+    <t>Communications &amp; Engagement Manager</t>
+  </si>
+  <si>
+    <t>International Economic Development Council (IEDC)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3e699cb4ae7444e96bb4a80bf5ac6c0-communications-engagement-manager-international-economic-development-council-iedc-washington</t>
+  </si>
+  <si>
+    <t>Community Growth Builder</t>
+  </si>
+  <si>
+    <t>USD 300.00 - 800.00/month</t>
+  </si>
+  <si>
+    <t>Media, Science Technology, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08f5fec3b5c340c9afbc2c85b122acd1-community-growth-builder-aeronord-media-seoul</t>
+  </si>
+  <si>
     <t>Community Organizer</t>
   </si>
   <si>
@@ -1084,6 +1318,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/37dbb3314f1c47e1863e5cbcb3846805-community-organizer-neighbors-together-kings-county</t>
   </si>
   <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>San Mateo, California</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/234295094f52469fac2bdc836379162c-controller-careers-in-nonprofits-inc-san-mateo</t>
+  </si>
+  <si>
     <t>Coordinator of Public Advancement</t>
   </si>
   <si>
@@ -1141,18 +1393,24 @@
     <t>https://www.idealist.org/en/job/e27ab62b5cbb4b1e8eec60103f2379db-deputy-director-of-program-operations-hera-washington</t>
   </si>
   <si>
+    <t>Deputy Director, Digital Communications, Unmoderated News</t>
+  </si>
+  <si>
+    <t>Third Way</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d869a3acdc204679aa5cffca6645f327-deputy-director-digital-communications-unmoderated-news-third-way-washington</t>
+  </si>
+  <si>
     <t>Deputy Director, Unmoderated News</t>
   </si>
   <si>
-    <t>Third Way</t>
-  </si>
-  <si>
-    <t>USD 105000.00 - 125000.00/year</t>
-  </si>
-  <si>
-    <t>Communications Access, Media</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d869a3acdc204679aa5cffca6645f327-deputy-director-unmoderated-news-third-way-washington</t>
   </si>
   <si>
@@ -1195,6 +1453,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/c2f1859d2b6f491cba3e6a64cedb7b75-development-coordinator-breakthrough-t1d-formerly-known-as-jdrf-winter-park</t>
   </si>
   <si>
+    <t>Kintsugi Village</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Family, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9458228f414c40ea848993b9ed8f959e-development-coordinator-kintsugi-village-detroit</t>
+  </si>
+  <si>
+    <t>Children's Center</t>
+  </si>
+  <si>
+    <t>Oregon City, OR</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 28.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/235f6807f8ce4d19a52ddb301f5c1aab-development-coordinator-childrens-center-oregon-city</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Liberty Economic Empowerment</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21add05305364a9b97d3ac8d1c0fb5cf-development-director-liberty-economic-empowerment-los-angeles</t>
+  </si>
+  <si>
     <t>Rocky Mountain Welcome Center</t>
   </si>
   <si>
@@ -1222,6 +1522,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/4a0042de17a64d99a9da9d7e180c94ab-development-operations-coordinator-new-york-common-pantry-new-york</t>
   </si>
   <si>
+    <t>Director - Institutional Development</t>
+  </si>
+  <si>
+    <t>Elevate</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 72500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/001f4a89ef184d8a9b87493d024fef6c-director-institutional-development-elevate-washington</t>
+  </si>
+  <si>
     <t>Director of Finance</t>
   </si>
   <si>
@@ -1240,6 +1552,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/60720f6be2f744199465acb3fdef37a6-director-of-finance-pace-womens-justice-center-white-plains</t>
   </si>
   <si>
+    <t>Director of Foundation Relations</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Civic Engagement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e453488fa294b84879e8df044e4dfbd-director-of-foundation-relations-food-water-watch-washington</t>
+  </si>
+  <si>
     <t>Director of Learning, Monitoring &amp; Evaluation</t>
   </si>
   <si>
@@ -1249,6 +1573,24 @@
     <t>https://www.idealist.org/en/job/6927f2c246894ba2bb5b1b12a1b38bd7-director-of-learning-monitoring-evaluation-hera-washington</t>
   </si>
   <si>
+    <t>Director, Colonias Water Project</t>
+  </si>
+  <si>
+    <t>DigDeep</t>
+  </si>
+  <si>
+    <t>El Paso, Texas</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 112000.00/year</t>
+  </si>
+  <si>
+    <t>Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/131d398aa18c49179fbe8def119fedd6-director-colonias-water-project-digdeep-el-paso</t>
+  </si>
+  <si>
     <t>Director, Policy &amp; Advocacy, Breakwater</t>
   </si>
   <si>
@@ -1279,6 +1621,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/c5c8c552798944a68ceaab708a22dc81-especialista-de-administracion-de-personal-payroll-eventual-medicos-sin-fronteras-lat-buenos-aires</t>
   </si>
   <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Westchester Youth Alliance</t>
+  </si>
+  <si>
+    <t>Westchester County, NY</t>
+  </si>
+  <si>
+    <t>USD 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d07d9180755f4b5ea323266b97f2a72c-executive-director-westchester-youth-alliance-westchester-county</t>
+  </si>
+  <si>
+    <t>Finance &amp; Compliance Director</t>
+  </si>
+  <si>
+    <t>Red Wine &amp; Blue</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00044fadb03d471abeb96e07188160a0-finance-compliance-director-red-wine-blue-cleveland</t>
+  </si>
+  <si>
     <t>Finance and Operations Associate</t>
   </si>
   <si>
@@ -1312,6 +1684,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/9d03ce7218f84e05a6d8c511aa5b3df9-financial-wellness-program-manager-homestretch-falls-church</t>
   </si>
   <si>
+    <t>Founding Operations &amp; Growth Specialist</t>
+  </si>
+  <si>
+    <t>PROJECT EDQUITY</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Race Ethnicity, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/dba0357558674359b13ec2adc7627439-founding-operations-growth-specialist-project-edquity-sacramento</t>
+  </si>
+  <si>
+    <t>FTE Program &amp; Culinary Support Specialist</t>
+  </si>
+  <si>
+    <t>Threshold Clubhouse</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95412831d17845a5a55c716d9a49d3d6-fte-program-culinary-support-specialist-threshold-clubhouse-durham</t>
+  </si>
+  <si>
     <t>Full-time Program Director</t>
   </si>
   <si>
@@ -1336,9 +1738,6 @@
     <t>USD 66500.00 - 68000.00/year</t>
   </si>
   <si>
-    <t>Mental Health, Seniors Retirement</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2da612b1798f4179aa294b9db460059c-geriatric-case-manager-greenwich-house-inc-kings-county</t>
   </si>
   <si>
@@ -1351,9 +1750,6 @@
     <t>Chelsea, Massachusetts</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 60.00 - 65.00/hour</t>
   </si>
   <si>
@@ -1375,9 +1771,6 @@
     <t>USD 18.00 - 25.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5387de6546ee4598bf18c8f834f98c02-group-leader-bronx-replications-inc-bronx</t>
   </si>
   <si>
@@ -1390,6 +1783,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c4b59900b36c49c1981a8734d2507965-group-leader-brooklyn-replications-inc-brooklyn</t>
   </si>
   <si>
+    <t>Internal and External Union Organizers</t>
+  </si>
+  <si>
+    <t>Service Employees International Union Local 925, Seattle</t>
+  </si>
+  <si>
+    <t>USD 80200.00 - 111870.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fea478b5d8b44fcb48f132cd1422808-internal-and-external-union-organizers-service-employees-international-union-local-925-seattle-seattle</t>
+  </si>
+  <si>
     <t>Large Scale Partnerships Manager (Wonder Grant)</t>
   </si>
   <si>
@@ -1405,6 +1813,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/180ed5a6188a4a3dbf66502f9c682931-large-scale-partnerships-manager-wonder-grant-rescuing-leftover-cuisine-new-york</t>
   </si>
   <si>
+    <t>Lead Assistant Video Editor</t>
+  </si>
+  <si>
+    <t>Block by Block Creative</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/be97e2177bf24815930873f129503bf0-lead-assistant-video-editor-block-by-block-creative-seattle</t>
+  </si>
+  <si>
+    <t>Legal Assistant</t>
+  </si>
+  <si>
+    <t>1199 SEIU United Healthcare Workers East</t>
+  </si>
+  <si>
+    <t>USD 79654.74/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d88b7e02bf444f76b23477c85c4e807a-legal-assistant-1199-seiu-united-healthcare-workers-east-new-york</t>
+  </si>
+  <si>
     <t>Legal Case Manager (Bilingual)</t>
   </si>
   <si>
@@ -1414,6 +1852,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/d2a8d206aed24e6692de6c825b4df779-legal-case-manager-bilingual-a-safe-place-waukegan</t>
   </si>
   <si>
+    <t>Legislative Fellow (Fall 2027)</t>
+  </si>
+  <si>
+    <t>Center for Reproductive Rights</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6163a83d0e9b4e33a9ec27bf778e8e78-legislative-fellow-fall-2027-center-for-reproductive-rights-new-york</t>
+  </si>
+  <si>
+    <t>Licensed Vocational Nurse</t>
+  </si>
+  <si>
+    <t>Pacific Asian Counseling Services</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58ac3ae46d2341f3b1143ed5cc155f3d-licensed-vocational-nurse-pacific-asian-counseling-services-los-angeles</t>
+  </si>
+  <si>
+    <t>Litigation Fellow (Fall 2027)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a78949e9bf5c45eeb539100555b2879e-litigation-fellow-fall-2027-center-for-reproductive-rights-new-york</t>
+  </si>
+  <si>
     <t>Major Gifts Officer</t>
   </si>
   <si>
@@ -1432,6 +1906,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/8a366083973f494fb206ec48cd10da09-major-gifts-officer-central-union-mission-riverdale-park</t>
   </si>
   <si>
+    <t>Major Taylor Project Coordinator - King County</t>
+  </si>
+  <si>
+    <t>Cascade Bicycle Club</t>
+  </si>
+  <si>
+    <t>USD 28.13 - 39.38/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70b93ca8a9684c5f9cddf788ea815b37-major-taylor-project-coordinator-king-county-cascade-bicycle-club-seattle</t>
+  </si>
+  <si>
     <t>Manager, Operations, Breakwater</t>
   </si>
   <si>
@@ -1471,6 +1960,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/96fc8f27c3d848ce9d03a1f926a26d09-managing-director-policy-breakwater-the-rockefeller-foundation-washington</t>
   </si>
   <si>
+    <t>Marketing &amp; Growth Manager</t>
+  </si>
+  <si>
+    <t>Challenge Success</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f41bb9d8b7a14a6385f77fa23dbca179-marketing-growth-manager-challenge-success-stanford</t>
+  </si>
+  <si>
+    <t>Marketing Officer</t>
+  </si>
+  <si>
+    <t>The San Francisco Foundation</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 144700.08 - 144700.08/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d9641e2a7cd48039e12c142bb9cd664-marketing-officer-the-san-francisco-foundation-san-francisco</t>
+  </si>
+  <si>
     <t>Nonprofit Finance Associate</t>
   </si>
   <si>
@@ -1549,6 +2068,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/35a4beea8ae54a4f980750c2212394fc-operations-associate-center-for-constitutional-rights-new-york</t>
   </si>
   <si>
+    <t>National Association of Women Lawyers</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6119e6fba5e24a83a23aba88dd7cfb41-operations-coordinator-national-association-of-women-lawyers-chicago</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3093e44fddc841c298d230ceb36da8d4-operations-manager-liberty-economic-empowerment-los-angeles</t>
+  </si>
+  <si>
     <t>Organizer in Training (Paid)</t>
   </si>
   <si>
@@ -1579,6 +2116,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/6fdc14a3243b495ca8871d4b918ce6f4-outcome-team-manager-friends-of-oakland-animal-services-oakland</t>
   </si>
   <si>
+    <t>Paralegal III, etc.</t>
+  </si>
+  <si>
+    <t>Washington State Bar Association (WSBA)</t>
+  </si>
+  <si>
+    <t>USD 64464.00 - 64464.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/04e2c3bc9a3743779c16eb86b193c277-paralegal-iii-etc-washington-state-bar-association-wsba-seattle</t>
+  </si>
+  <si>
+    <t>Part Time Finance Assistant</t>
+  </si>
+  <si>
+    <t>Lower Manhattan Cultural Council</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a58cc34ed71c4aa1839b487def2bf36d-part-time-finance-assistant-lower-manhattan-cultural-council-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Pastoral Minister for Young Adults</t>
+  </si>
+  <si>
+    <t>The Paulist Center</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/884d8362497449cdafb6a4e28b56cb31-part-time-pastoral-minister-for-young-adults-the-paulist-center-boston</t>
+  </si>
+  <si>
+    <t>Partnerships &amp; Growth Associate, Greater Seattle (Part-Time/Temporary)</t>
+  </si>
+  <si>
+    <t>Reading Partners</t>
+  </si>
+  <si>
+    <t>USD 26.27 - 30.91/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/843e0378142949cd89a69d38ffef51e4-partnerships-growth-associate-greater-seattle-part-timetemporary-reading-partners-oakland</t>
+  </si>
+  <si>
     <t>Portfolio Associate</t>
   </si>
   <si>
@@ -1615,9 +2212,6 @@
     <t>Seattle PlayGarden</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 24.00 - 26.00/hour</t>
   </si>
   <si>
@@ -1639,6 +2233,24 @@
     <t>https://www.idealist.org/en/job/f0700d7a44914706a556247f11ca5dfc-president-ceo-mid-ohio-food-collective-grove-city</t>
   </si>
   <si>
+    <t>Professional Mentor - Chicago</t>
+  </si>
+  <si>
+    <t>Friends of the Children - Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 57717.00 - 57717.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08faf0520a114c809f932c00e6aa5a9a-professional-mentor-chicago-friends-of-the-children-chicago-chicago</t>
+  </si>
+  <si>
     <t>PROGRAM ASSOCIATE</t>
   </si>
   <si>
@@ -1675,6 +2287,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/318cd3c45b974d82907033d26ebf3103-program-associate-strategic-initiatives-naacp-legal-defense-and-educational-fund-inc-new-york</t>
   </si>
   <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Partnership with Children</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2e9ba79488f43bbb92c936e3022d60a-program-director-partnership-with-children-bronx</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b18ec97c1f0f4c37a95267c9b942a26f-program-director-partnership-with-children-brooklyn</t>
+  </si>
+  <si>
+    <t>Program Manager, Technology and International Affairs Program</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 82500.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96b0f8bee7084003837405f500210323-program-manager-technology-and-international-affairs-program-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
     <t>Program Support Coordinator</t>
   </si>
   <si>
@@ -1690,6 +2335,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/c1970d5530c7426e90a8cb75b8dd2eb1-program-support-coordinator-california-it-in-education-cite-sacramento</t>
   </si>
   <si>
+    <t>Request for Proposals: Contracted Bookkeeper</t>
+  </si>
+  <si>
+    <t>Take This</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd3b5f53d3d945ddbbbc8059dae2d671-request-for-proposals-contracted-bookkeeper-take-this-kirkland</t>
+  </si>
+  <si>
     <t>Senior Administrative Coordinator, Programs &amp; Services</t>
   </si>
   <si>
@@ -1705,6 +2359,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/a1b5a725577245cd8f9a53a38e0db34c-senior-administrative-coordinator-programs-services-nami-national-alliance-on-mental-illness-arlington</t>
   </si>
   <si>
+    <t>Senior Associate (Climate Solutions)</t>
+  </si>
+  <si>
+    <t>CEA Consulting</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/f5cdbdc8e1344eb5817a2b126232fb61-senior-associate-climate-solutions-cea-consulting-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Development Manager</t>
+  </si>
+  <si>
+    <t>First Graduate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6178b44b3324450a97a869282ba6ba7-senior-development-manager-first-graduate-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Development Manager, Special Events</t>
+  </si>
+  <si>
+    <t>Basking Ridge, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/95e2dfa3210b48fdae4f0023caa24085-senior-development-manager-special-events-careers-in-nonprofits-inc-basking-ridge</t>
+  </si>
+  <si>
     <t>Senior Fundraising Copywriter</t>
   </si>
   <si>
@@ -1741,6 +2431,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e2b08f36954a4173b7b17c2d2574677d-senior-operations-manager-california-it-in-education-cite-sacramento</t>
   </si>
   <si>
+    <t>Senior Policy Counsel</t>
+  </si>
+  <si>
+    <t>Toxic-Free Future</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65bf36caff944188a50c9530c17b7e14-senior-policy-counsel-toxic-free-future-seattle</t>
+  </si>
+  <si>
     <t>Senior Project Manager or Project Manager</t>
   </si>
   <si>
@@ -1774,6 +2479,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/104642f06bbe460eba09d077c919ec07-social-work-lead-manager-vast-bc-vancouver-association-for-survivors-of-torture-surrey</t>
   </si>
   <si>
+    <t>Social Work Supervisor</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd542b5e8bfc489981f7bd2bbff6d748-social-work-supervisor-east-side-house-settlement-bronx</t>
+  </si>
+  <si>
     <t>Special Assistant to the CEO, Breakwater</t>
   </si>
   <si>
@@ -1804,18 +2527,12 @@
     <t>Council on American-Islamic Relations, New York Chapter (CAIR-NY)</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e5bb6d34f27a4f2191082f35d42bc474-staff-attorney-council-on-american-islamic-relations-new-york-chapter-cair-ny-new-york</t>
   </si>
   <si>
     <t>Cesar Chavez Foundation</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 100000.00 - 150000.00/year</t>
   </si>
   <si>
@@ -1825,6 +2542,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/210500305da144afb125b3dd6e88fb5d-staff-attorney-cesar-chavez-foundation-los-angeles</t>
   </si>
   <si>
+    <t>Disability Rights New York</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be1cf4050fba4248818ec3ba4d785fc7-staff-attorney-disability-rights-new-york-brooklyn</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12441f0e763b4648895474cbfe7e8133-staff-attorney-disability-rights-new-york-rochester</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1434acab2b884ee984f0a3fbb83fec79-staff-attorney-disability-rights-new-york-albany</t>
+  </si>
+  <si>
+    <t>Staff Attorney (CA)</t>
+  </si>
+  <si>
+    <t>Disability Rights Advocates</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 93627.00 - 116877.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90bdcd3fade64c7d8e1a91e98cebf59b-staff-attorney-ca-disability-rights-advocates-berkeley</t>
+  </si>
+  <si>
+    <t>Staff Attorney (NY)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc38cbe98b374a5c8858e169908397c4-staff-attorney-ny-disability-rights-advocates-new-york</t>
+  </si>
+  <si>
     <t>Strategic Finance Director</t>
   </si>
   <si>
@@ -1834,12 +2599,36 @@
     <t>USD 109180.00 - 142000.00/year</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9a282262a87b4239aab1599551f47ed4-strategic-finance-director-donorschoose-new-york</t>
   </si>
   <si>
+    <t>Temporary Immigration Paralegal -- Victims' Services</t>
+  </si>
+  <si>
+    <t>Community Justice Project</t>
+  </si>
+  <si>
+    <t>Reading, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Victim Support, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec31a4053f514a8aad61994303d541bf-temporary-immigration-paralegal-victims-services-community-justice-project-reading</t>
+  </si>
+  <si>
+    <t>Vice President of Fund Development</t>
+  </si>
+  <si>
+    <t>Essential Access Health</t>
+  </si>
+  <si>
+    <t>USD 150087.00 - 150087.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ddbe5c42194048ebbdf557b950420f14-vice-president-of-fund-development-essential-access-health-los-angeles</t>
+  </si>
+  <si>
     <t>Vice President, Mobilization and Generosity</t>
   </si>
   <si>
@@ -1852,6 +2641,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5852e4b8cc2744b682a1442c255c748b-vice-president-mobilization-and-generosity-hope-for-new-york-new-york</t>
   </si>
   <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Travelers Aid International</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/820024054a2a47deb5e9689fffb72f6e-volunteer-coordinator-travelers-aid-international-arlington</t>
+  </si>
+  <si>
     <t>Wellbeing Navigator</t>
   </si>
   <si>
@@ -1868,6 +2672,24 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/1afad37947924626833a7bfe79c1ccf0-wellbeing-navigator-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Wish Assist Manager</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Mid-Atlantic: Bethesda office</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8880aeda2aef45e784fe07599a78a4da-wish-assist-manager-make-a-wish-mid-atlantic-bethesda-office-bethesda</t>
   </si>
   <si>
     <t>Youth Employment Specialist</t>
@@ -3506,7 +4328,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3579,128 +4401,128 @@
         <v>245</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" t="s">
         <v>255</v>
       </c>
-      <c r="B5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="H5" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="D5" t="s">
-        <v>258</v>
-      </c>
-      <c r="E5" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" t="s">
-        <v>260</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F6" t="s">
         <v>262</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H6" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="C6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D6" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" t="s">
-        <v>265</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" t="s">
         <v>267</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
         <v>268</v>
       </c>
-      <c r="C7" t="s">
+      <c r="H7" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="D7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" t="s">
         <v>272</v>
       </c>
-      <c r="B8" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" t="s">
         <v>273</v>
       </c>
-      <c r="D8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>274</v>
-      </c>
-      <c r="F8" t="s">
-        <v>247</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>275</v>
@@ -3717,174 +4539,174 @@
         <v>278</v>
       </c>
       <c r="D9" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E9" t="s">
         <v>279</v>
       </c>
       <c r="F9" t="s">
+        <v>268</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" t="s">
         <v>282</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>283</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F10" t="s">
         <v>284</v>
       </c>
-      <c r="D10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="H10" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="F10" t="s">
-        <v>253</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" t="s">
         <v>287</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>288</v>
       </c>
-      <c r="C11" t="s">
-        <v>269</v>
-      </c>
       <c r="D11" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" t="s">
         <v>289</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" t="s">
         <v>292</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" t="s">
         <v>293</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
+        <v>268</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D12" t="s">
-        <v>239</v>
-      </c>
-      <c r="E12" t="s">
-        <v>295</v>
-      </c>
-      <c r="F12" t="s">
-        <v>296</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F13" t="s">
+        <v>262</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="B13" t="s">
-        <v>299</v>
-      </c>
-      <c r="C13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" t="s">
-        <v>239</v>
-      </c>
-      <c r="E13" t="s">
-        <v>301</v>
-      </c>
-      <c r="F13" t="s">
-        <v>302</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" t="s">
+        <v>302</v>
+      </c>
+      <c r="F14" t="s">
+        <v>303</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="B14" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" t="s">
-        <v>306</v>
-      </c>
-      <c r="D14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" t="s">
-        <v>307</v>
-      </c>
-      <c r="F14" t="s">
-        <v>308</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E15" t="s">
+        <v>308</v>
+      </c>
+      <c r="F15" t="s">
+        <v>309</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B15" t="s">
-        <v>277</v>
-      </c>
-      <c r="C15" t="s">
-        <v>278</v>
-      </c>
-      <c r="D15" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" t="s">
-        <v>311</v>
-      </c>
-      <c r="F15" t="s">
-        <v>280</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C16" t="s">
         <v>313</v>
       </c>
-      <c r="B16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C16" t="s">
-        <v>278</v>
-      </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E16" t="s">
         <v>314</v>
       </c>
       <c r="F16" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>315</v>
@@ -3901,7 +4723,7 @@
         <v>318</v>
       </c>
       <c r="D17" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="E17" t="s">
         <v>319</v>
@@ -3921,177 +4743,177 @@
         <v>323</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E18" t="s">
         <v>324</v>
       </c>
       <c r="F18" t="s">
+        <v>320</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>326</v>
+      </c>
+      <c r="B19" t="s">
         <v>327</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>328</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>246</v>
+      </c>
+      <c r="E19" t="s">
         <v>329</v>
       </c>
-      <c r="D19" t="s">
-        <v>239</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>268</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="F19" t="s">
-        <v>331</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>331</v>
+      </c>
+      <c r="B20" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" t="s">
+        <v>278</v>
+      </c>
+      <c r="D20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" t="s">
         <v>333</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" t="s">
         <v>334</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="D20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E20" t="s">
-        <v>336</v>
-      </c>
-      <c r="F20" t="s">
-        <v>253</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" t="s">
+        <v>246</v>
+      </c>
+      <c r="E21" t="s">
         <v>338</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>339</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="D21" t="s">
-        <v>341</v>
-      </c>
-      <c r="E21" t="s">
-        <v>342</v>
-      </c>
-      <c r="F21" t="s">
-        <v>343</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>341</v>
+      </c>
+      <c r="B22" t="s">
+        <v>342</v>
+      </c>
+      <c r="C22" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" t="s">
+        <v>344</v>
+      </c>
+      <c r="F22" t="s">
         <v>345</v>
       </c>
-      <c r="B22" t="s">
+      <c r="H22" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="C22" t="s">
-        <v>347</v>
-      </c>
-      <c r="D22" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" t="s">
-        <v>348</v>
-      </c>
-      <c r="F22" t="s">
-        <v>349</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B23" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C23" t="s">
         <v>278</v>
       </c>
       <c r="D23" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E23" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F23" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>352</v>
+      </c>
+      <c r="B24" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" t="s">
+        <v>354</v>
+      </c>
+      <c r="D24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E24" t="s">
+        <v>355</v>
+      </c>
+      <c r="F24" t="s">
         <v>356</v>
       </c>
-      <c r="B24" t="s">
+      <c r="H24" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="C24" t="s">
-        <v>358</v>
-      </c>
-      <c r="D24" t="s">
-        <v>239</v>
-      </c>
-      <c r="E24" t="s">
-        <v>252</v>
-      </c>
-      <c r="F24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>358</v>
+      </c>
+      <c r="B25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C25" t="s">
         <v>360</v>
-      </c>
-      <c r="B25" t="s">
-        <v>361</v>
-      </c>
-      <c r="C25" t="s">
-        <v>362</v>
       </c>
       <c r="D25" t="s">
         <v>239</v>
       </c>
       <c r="E25" t="s">
-        <v>253</v>
+        <v>361</v>
       </c>
       <c r="F25" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>363</v>
@@ -4108,7 +4930,7 @@
         <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
         <v>367</v>
@@ -4125,456 +4947,456 @@
         <v>370</v>
       </c>
       <c r="B27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C27" t="s">
+        <v>301</v>
+      </c>
+      <c r="D27" t="s">
+        <v>246</v>
+      </c>
+      <c r="E27" t="s">
         <v>371</v>
       </c>
-      <c r="C27" t="s">
-        <v>347</v>
-      </c>
-      <c r="D27" t="s">
-        <v>239</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>303</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="F27" t="s">
-        <v>373</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>373</v>
+      </c>
+      <c r="B28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C28" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" t="s">
+        <v>246</v>
+      </c>
+      <c r="E28" t="s">
+        <v>374</v>
+      </c>
+      <c r="F28" t="s">
+        <v>303</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="B28" t="s">
-        <v>376</v>
-      </c>
-      <c r="C28" t="s">
-        <v>340</v>
-      </c>
-      <c r="D28" t="s">
-        <v>239</v>
-      </c>
-      <c r="E28" t="s">
-        <v>377</v>
-      </c>
-      <c r="F28" t="s">
-        <v>378</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>376</v>
+      </c>
+      <c r="B29" t="s">
+        <v>377</v>
+      </c>
+      <c r="C29" t="s">
+        <v>378</v>
+      </c>
+      <c r="D29" t="s">
+        <v>379</v>
+      </c>
+      <c r="E29" t="s">
         <v>380</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F29" t="s">
         <v>381</v>
       </c>
-      <c r="C29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" t="s">
-        <v>239</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="H29" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="F29" t="s">
-        <v>383</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C30" t="s">
         <v>385</v>
       </c>
-      <c r="B30" t="s">
-        <v>250</v>
-      </c>
-      <c r="C30" t="s">
-        <v>251</v>
-      </c>
       <c r="D30" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E30" t="s">
-        <v>252</v>
+        <v>386</v>
       </c>
       <c r="F30" t="s">
-        <v>253</v>
+        <v>387</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C31" t="s">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>394</v>
       </c>
       <c r="B32" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D32" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="E32" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E33" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F33" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B34" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C34" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D34" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B35" t="s">
-        <v>371</v>
+        <v>411</v>
       </c>
       <c r="C35" t="s">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="D35" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="E35" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F35" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C36" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D36" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E36" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F36" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B37" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C37" t="s">
-        <v>418</v>
+        <v>360</v>
       </c>
       <c r="D37" t="s">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="E37" t="s">
-        <v>253</v>
+        <v>422</v>
       </c>
       <c r="F37" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B38" t="s">
-        <v>422</v>
+        <v>359</v>
       </c>
       <c r="C38" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="D38" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E38" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F38" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B39" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C39" t="s">
-        <v>429</v>
+        <v>301</v>
       </c>
       <c r="D39" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E39" t="s">
-        <v>252</v>
+        <v>431</v>
       </c>
       <c r="F39" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B40" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C40" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D40" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E40" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F40" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>441</v>
       </c>
       <c r="C41" t="s">
-        <v>278</v>
+        <v>442</v>
       </c>
       <c r="D41" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E41" t="s">
-        <v>439</v>
+        <v>267</v>
       </c>
       <c r="F41" t="s">
-        <v>440</v>
+        <v>268</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B42" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C42" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D42" t="s">
-        <v>445</v>
+        <v>246</v>
       </c>
       <c r="E42" t="s">
-        <v>446</v>
+        <v>268</v>
       </c>
       <c r="F42" t="s">
+        <v>268</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>448</v>
+      </c>
+      <c r="B43" t="s">
         <v>449</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>450</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
+        <v>246</v>
+      </c>
+      <c r="E43" t="s">
         <v>451</v>
       </c>
-      <c r="D43" t="s">
-        <v>258</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>452</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>454</v>
+      </c>
+      <c r="B44" t="s">
         <v>455</v>
       </c>
-      <c r="B44" t="s">
-        <v>450</v>
-      </c>
       <c r="C44" t="s">
+        <v>360</v>
+      </c>
+      <c r="D44" t="s">
+        <v>246</v>
+      </c>
+      <c r="E44" t="s">
         <v>456</v>
       </c>
-      <c r="D44" t="s">
-        <v>258</v>
-      </c>
-      <c r="E44" t="s">
-        <v>452</v>
-      </c>
       <c r="F44" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B45" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C45" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="D45" t="s">
-        <v>445</v>
+        <v>246</v>
       </c>
       <c r="E45" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F45" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B46" t="s">
-        <v>293</v>
+        <v>460</v>
       </c>
       <c r="C46" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D46" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E46" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F46" t="s">
-        <v>296</v>
+        <v>462</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>465</v>
@@ -4588,131 +5410,131 @@
         <v>467</v>
       </c>
       <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" t="s">
         <v>468</v>
       </c>
-      <c r="D47" t="s">
-        <v>239</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>469</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>471</v>
+      </c>
+      <c r="B48" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" t="s">
+        <v>266</v>
+      </c>
+      <c r="D48" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F48" t="s">
+        <v>268</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="B48" t="s">
-        <v>412</v>
-      </c>
-      <c r="C48" t="s">
-        <v>340</v>
-      </c>
-      <c r="D48" t="s">
-        <v>239</v>
-      </c>
-      <c r="E48" t="s">
-        <v>473</v>
-      </c>
-      <c r="F48" t="s">
-        <v>474</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>473</v>
+      </c>
+      <c r="B49" t="s">
+        <v>474</v>
+      </c>
+      <c r="C49" t="s">
+        <v>475</v>
+      </c>
+      <c r="D49" t="s">
+        <v>246</v>
+      </c>
+      <c r="E49" t="s">
         <v>476</v>
       </c>
-      <c r="B49" t="s">
+      <c r="F49" t="s">
         <v>477</v>
       </c>
-      <c r="C49" t="s">
-        <v>269</v>
-      </c>
-      <c r="D49" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="H49" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="F49" t="s">
-        <v>479</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>473</v>
+      </c>
+      <c r="B50" t="s">
+        <v>479</v>
+      </c>
+      <c r="C50" t="s">
+        <v>480</v>
+      </c>
+      <c r="D50" t="s">
+        <v>246</v>
+      </c>
+      <c r="E50" t="s">
         <v>481</v>
       </c>
-      <c r="B50" t="s">
-        <v>412</v>
-      </c>
-      <c r="C50" t="s">
-        <v>340</v>
-      </c>
-      <c r="D50" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>482</v>
       </c>
-      <c r="F50" t="s">
+      <c r="H50" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>473</v>
+      </c>
+      <c r="B51" t="s">
+        <v>484</v>
+      </c>
+      <c r="C51" t="s">
         <v>485</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
+        <v>246</v>
+      </c>
+      <c r="E51" t="s">
         <v>486</v>
       </c>
-      <c r="C51" t="s">
-        <v>347</v>
-      </c>
-      <c r="D51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
+        <v>268</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="F51" t="s">
-        <v>488</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>488</v>
+      </c>
+      <c r="B52" t="s">
+        <v>489</v>
+      </c>
+      <c r="C52" t="s">
+        <v>288</v>
+      </c>
+      <c r="D52" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" t="s">
         <v>490</v>
       </c>
-      <c r="B52" t="s">
-        <v>486</v>
-      </c>
-      <c r="C52" t="s">
-        <v>347</v>
-      </c>
-      <c r="D52" t="s">
-        <v>239</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>491</v>
-      </c>
-      <c r="F52" t="s">
-        <v>488</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>492</v>
@@ -4720,692 +5542,2118 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" t="s">
         <v>493</v>
       </c>
-      <c r="B53" t="s">
-        <v>486</v>
-      </c>
       <c r="C53" t="s">
-        <v>347</v>
+        <v>494</v>
       </c>
       <c r="D53" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E53" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F53" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B54" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="C54" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="D54" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E54" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="F54" t="s">
-        <v>488</v>
+        <v>268</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B55" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C55" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D55" t="s">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="E55" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="F55" t="s">
-        <v>500</v>
+        <v>268</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B56" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C56" t="s">
-        <v>340</v>
+        <v>508</v>
       </c>
       <c r="D56" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E56" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F56" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s">
-        <v>507</v>
+        <v>377</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="D57" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="E57" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F57" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B58" t="s">
-        <v>512</v>
+        <v>455</v>
       </c>
       <c r="C58" t="s">
-        <v>513</v>
+        <v>360</v>
       </c>
       <c r="D58" t="s">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="E58" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F58" t="s">
-        <v>515</v>
+        <v>457</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C59" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="D59" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E59" t="s">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="F59" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C60" t="s">
-        <v>523</v>
+        <v>307</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E60" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F60" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>144</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C61" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D61" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="E61" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="F61" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B62" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C62" t="s">
-        <v>306</v>
+        <v>537</v>
       </c>
       <c r="D62" t="s">
-        <v>533</v>
+        <v>253</v>
       </c>
       <c r="E62" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F62" t="s">
-        <v>535</v>
+        <v>387</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B63" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C63" t="s">
-        <v>539</v>
+        <v>360</v>
       </c>
       <c r="D63" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E63" t="s">
-        <v>253</v>
+        <v>542</v>
       </c>
       <c r="F63" t="s">
-        <v>253</v>
+        <v>543</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B64" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C64" t="s">
-        <v>269</v>
+        <v>547</v>
       </c>
       <c r="D64" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E64" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F64" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B65" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C65" t="s">
-        <v>340</v>
+        <v>553</v>
       </c>
       <c r="D65" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E65" t="s">
-        <v>548</v>
+        <v>267</v>
       </c>
       <c r="F65" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="B66" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="C66" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="D66" t="s">
         <v>239</v>
       </c>
       <c r="E66" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F66" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B67" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C67" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D67" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E67" t="s">
-        <v>503</v>
+        <v>349</v>
       </c>
       <c r="F67" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B68" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C68" t="s">
-        <v>347</v>
+        <v>568</v>
       </c>
       <c r="D68" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E68" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="F68" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B69" t="s">
-        <v>564</v>
+        <v>300</v>
       </c>
       <c r="C69" t="s">
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="D69" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E69" t="s">
-        <v>469</v>
+        <v>573</v>
       </c>
       <c r="F69" t="s">
-        <v>253</v>
+        <v>350</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B70" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="C70" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="D70" t="s">
         <v>239</v>
       </c>
       <c r="E70" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="F70" t="s">
-        <v>320</v>
+        <v>579</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B71" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="C71" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="D71" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E71" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F71" t="s">
-        <v>573</v>
+        <v>438</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="B72" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C72" t="s">
-        <v>329</v>
+        <v>587</v>
       </c>
       <c r="D72" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E72" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F72" t="s">
-        <v>578</v>
+        <v>438</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="B73" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="C73" t="s">
-        <v>582</v>
+        <v>366</v>
       </c>
       <c r="D73" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E73" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="F73" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B74" t="s">
-        <v>412</v>
+        <v>595</v>
       </c>
       <c r="C74" t="s">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="D74" t="s">
         <v>239</v>
       </c>
       <c r="E74" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="F74" t="s">
-        <v>474</v>
+        <v>597</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="B75" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="C75" t="s">
-        <v>591</v>
+        <v>360</v>
       </c>
       <c r="D75" t="s">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="E75" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="F75" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="B76" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="C76" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D76" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E76" t="s">
-        <v>289</v>
+        <v>606</v>
       </c>
       <c r="F76" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="B77" t="s">
-        <v>598</v>
+        <v>342</v>
       </c>
       <c r="C77" t="s">
-        <v>599</v>
+        <v>343</v>
       </c>
       <c r="D77" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E77" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="F77" t="s">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="B78" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="C78" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="D78" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E78" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="F78" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="B79" t="s">
-        <v>477</v>
+        <v>618</v>
       </c>
       <c r="C79" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="D79" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E79" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="F79" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="B80" t="s">
         <v>613</v>
       </c>
       <c r="C80" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" t="s">
+        <v>246</v>
+      </c>
+      <c r="E80" t="s">
         <v>614</v>
       </c>
-      <c r="D80" t="s">
-        <v>239</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>615</v>
       </c>
-      <c r="F80" t="s">
-        <v>616</v>
-      </c>
       <c r="H80" s="2" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B81" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C81" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D81" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E81" t="s">
-        <v>503</v>
+        <v>627</v>
       </c>
       <c r="F81" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B82" t="s">
-        <v>443</v>
+        <v>631</v>
       </c>
       <c r="C82" t="s">
-        <v>444</v>
+        <v>10</v>
       </c>
       <c r="D82" t="s">
+        <v>246</v>
+      </c>
+      <c r="E82" t="s">
+        <v>632</v>
+      </c>
+      <c r="F82" t="s">
+        <v>633</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>635</v>
+      </c>
+      <c r="B83" t="s">
+        <v>526</v>
+      </c>
+      <c r="C83" t="s">
+        <v>307</v>
+      </c>
+      <c r="D83" t="s">
+        <v>246</v>
+      </c>
+      <c r="E83" t="s">
+        <v>636</v>
+      </c>
+      <c r="F83" t="s">
+        <v>637</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>639</v>
+      </c>
+      <c r="B84" t="s">
+        <v>640</v>
+      </c>
+      <c r="C84" t="s">
+        <v>278</v>
+      </c>
+      <c r="D84" t="s">
+        <v>246</v>
+      </c>
+      <c r="E84" t="s">
+        <v>641</v>
+      </c>
+      <c r="F84" t="s">
+        <v>642</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>644</v>
+      </c>
+      <c r="B85" t="s">
+        <v>526</v>
+      </c>
+      <c r="C85" t="s">
+        <v>307</v>
+      </c>
+      <c r="D85" t="s">
+        <v>246</v>
+      </c>
+      <c r="E85" t="s">
+        <v>645</v>
+      </c>
+      <c r="F85" t="s">
+        <v>646</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>648</v>
+      </c>
+      <c r="B86" t="s">
+        <v>649</v>
+      </c>
+      <c r="C86" t="s">
+        <v>360</v>
+      </c>
+      <c r="D86" t="s">
+        <v>246</v>
+      </c>
+      <c r="E86" t="s">
+        <v>422</v>
+      </c>
+      <c r="F86" t="s">
+        <v>650</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>652</v>
+      </c>
+      <c r="B87" t="s">
+        <v>653</v>
+      </c>
+      <c r="C87" t="s">
+        <v>654</v>
+      </c>
+      <c r="D87" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" t="s">
+        <v>655</v>
+      </c>
+      <c r="F87" t="s">
+        <v>656</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>658</v>
+      </c>
+      <c r="B88" t="s">
+        <v>659</v>
+      </c>
+      <c r="C88" t="s">
+        <v>360</v>
+      </c>
+      <c r="D88" t="s">
+        <v>253</v>
+      </c>
+      <c r="E88" t="s">
+        <v>660</v>
+      </c>
+      <c r="F88" t="s">
+        <v>661</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>663</v>
+      </c>
+      <c r="B89" t="s">
+        <v>659</v>
+      </c>
+      <c r="C89" t="s">
+        <v>360</v>
+      </c>
+      <c r="D89" t="s">
+        <v>246</v>
+      </c>
+      <c r="E89" t="s">
+        <v>664</v>
+      </c>
+      <c r="F89" t="s">
+        <v>661</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>666</v>
+      </c>
+      <c r="B90" t="s">
+        <v>659</v>
+      </c>
+      <c r="C90" t="s">
+        <v>360</v>
+      </c>
+      <c r="D90" t="s">
+        <v>246</v>
+      </c>
+      <c r="E90" t="s">
+        <v>667</v>
+      </c>
+      <c r="F90" t="s">
+        <v>661</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>669</v>
+      </c>
+      <c r="B91" t="s">
+        <v>659</v>
+      </c>
+      <c r="C91" t="s">
+        <v>360</v>
+      </c>
+      <c r="D91" t="s">
+        <v>246</v>
+      </c>
+      <c r="E91" t="s">
+        <v>667</v>
+      </c>
+      <c r="F91" t="s">
+        <v>661</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>671</v>
+      </c>
+      <c r="B92" t="s">
+        <v>672</v>
+      </c>
+      <c r="C92" t="s">
+        <v>307</v>
+      </c>
+      <c r="D92" t="s">
+        <v>379</v>
+      </c>
+      <c r="E92" t="s">
+        <v>660</v>
+      </c>
+      <c r="F92" t="s">
+        <v>673</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>675</v>
+      </c>
+      <c r="B93" t="s">
+        <v>672</v>
+      </c>
+      <c r="C93" t="s">
+        <v>307</v>
+      </c>
+      <c r="D93" t="s">
+        <v>246</v>
+      </c>
+      <c r="E93" t="s">
+        <v>676</v>
+      </c>
+      <c r="F93" t="s">
+        <v>677</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>679</v>
+      </c>
+      <c r="B94" t="s">
+        <v>680</v>
+      </c>
+      <c r="C94" t="s">
+        <v>278</v>
+      </c>
+      <c r="D94" t="s">
+        <v>253</v>
+      </c>
+      <c r="E94" t="s">
+        <v>681</v>
+      </c>
+      <c r="F94" t="s">
+        <v>682</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>133</v>
+      </c>
+      <c r="B95" t="s">
+        <v>684</v>
+      </c>
+      <c r="C95" t="s">
+        <v>360</v>
+      </c>
+      <c r="D95" t="s">
+        <v>246</v>
+      </c>
+      <c r="E95" t="s">
+        <v>685</v>
+      </c>
+      <c r="F95" t="s">
+        <v>268</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>687</v>
+      </c>
+      <c r="B96" t="s">
+        <v>489</v>
+      </c>
+      <c r="C96" t="s">
+        <v>288</v>
+      </c>
+      <c r="D96" t="s">
+        <v>246</v>
+      </c>
+      <c r="E96" t="s">
+        <v>688</v>
+      </c>
+      <c r="F96" t="s">
+        <v>491</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>690</v>
+      </c>
+      <c r="B97" t="s">
+        <v>691</v>
+      </c>
+      <c r="C97" t="s">
+        <v>692</v>
+      </c>
+      <c r="D97" t="s">
+        <v>379</v>
+      </c>
+      <c r="E97" t="s">
+        <v>693</v>
+      </c>
+      <c r="F97" t="s">
+        <v>694</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>696</v>
+      </c>
+      <c r="B98" t="s">
+        <v>697</v>
+      </c>
+      <c r="C98" t="s">
+        <v>692</v>
+      </c>
+      <c r="D98" t="s">
+        <v>246</v>
+      </c>
+      <c r="E98" t="s">
+        <v>641</v>
+      </c>
+      <c r="F98" t="s">
+        <v>698</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>700</v>
+      </c>
+      <c r="B99" t="s">
+        <v>701</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>246</v>
+      </c>
+      <c r="E99" t="s">
+        <v>702</v>
+      </c>
+      <c r="F99" t="s">
+        <v>703</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>705</v>
+      </c>
+      <c r="B100" t="s">
+        <v>706</v>
+      </c>
+      <c r="C100" t="s">
+        <v>278</v>
+      </c>
+      <c r="D100" t="s">
+        <v>707</v>
+      </c>
+      <c r="E100" t="s">
+        <v>708</v>
+      </c>
+      <c r="F100" t="s">
+        <v>709</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>711</v>
+      </c>
+      <c r="B101" t="s">
+        <v>712</v>
+      </c>
+      <c r="C101" t="s">
+        <v>396</v>
+      </c>
+      <c r="D101" t="s">
+        <v>253</v>
+      </c>
+      <c r="E101" t="s">
+        <v>268</v>
+      </c>
+      <c r="F101" t="s">
+        <v>713</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>715</v>
+      </c>
+      <c r="B102" t="s">
+        <v>716</v>
+      </c>
+      <c r="C102" t="s">
+        <v>692</v>
+      </c>
+      <c r="D102" t="s">
+        <v>253</v>
+      </c>
+      <c r="E102" t="s">
+        <v>717</v>
+      </c>
+      <c r="F102" t="s">
+        <v>718</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>720</v>
+      </c>
+      <c r="B103" t="s">
+        <v>721</v>
+      </c>
+      <c r="C103" t="s">
+        <v>722</v>
+      </c>
+      <c r="D103" t="s">
+        <v>246</v>
+      </c>
+      <c r="E103" t="s">
+        <v>723</v>
+      </c>
+      <c r="F103" t="s">
+        <v>724</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>144</v>
+      </c>
+      <c r="B104" t="s">
+        <v>726</v>
+      </c>
+      <c r="C104" t="s">
+        <v>727</v>
+      </c>
+      <c r="D104" t="s">
+        <v>246</v>
+      </c>
+      <c r="E104" t="s">
+        <v>268</v>
+      </c>
+      <c r="F104" t="s">
+        <v>728</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>730</v>
+      </c>
+      <c r="B105" t="s">
+        <v>731</v>
+      </c>
+      <c r="C105" t="s">
+        <v>366</v>
+      </c>
+      <c r="D105" t="s">
+        <v>707</v>
+      </c>
+      <c r="E105" t="s">
+        <v>732</v>
+      </c>
+      <c r="F105" t="s">
+        <v>733</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>735</v>
+      </c>
+      <c r="B106" t="s">
+        <v>736</v>
+      </c>
+      <c r="C106" t="s">
+        <v>737</v>
+      </c>
+      <c r="D106" t="s">
+        <v>246</v>
+      </c>
+      <c r="E106" t="s">
+        <v>268</v>
+      </c>
+      <c r="F106" t="s">
+        <v>268</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>739</v>
+      </c>
+      <c r="B107" t="s">
+        <v>740</v>
+      </c>
+      <c r="C107" t="s">
+        <v>741</v>
+      </c>
+      <c r="D107" t="s">
+        <v>246</v>
+      </c>
+      <c r="E107" t="s">
+        <v>742</v>
+      </c>
+      <c r="F107" t="s">
+        <v>743</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>745</v>
+      </c>
+      <c r="B108" t="s">
+        <v>746</v>
+      </c>
+      <c r="C108" t="s">
+        <v>278</v>
+      </c>
+      <c r="D108" t="s">
+        <v>246</v>
+      </c>
+      <c r="E108" t="s">
+        <v>747</v>
+      </c>
+      <c r="F108" t="s">
+        <v>748</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>750</v>
+      </c>
+      <c r="B109" t="s">
+        <v>751</v>
+      </c>
+      <c r="C109" t="s">
+        <v>307</v>
+      </c>
+      <c r="D109" t="s">
+        <v>246</v>
+      </c>
+      <c r="E109" t="s">
+        <v>752</v>
+      </c>
+      <c r="F109" t="s">
+        <v>753</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>750</v>
+      </c>
+      <c r="B110" t="s">
+        <v>751</v>
+      </c>
+      <c r="C110" t="s">
+        <v>278</v>
+      </c>
+      <c r="D110" t="s">
+        <v>246</v>
+      </c>
+      <c r="E110" t="s">
+        <v>755</v>
+      </c>
+      <c r="F110" t="s">
+        <v>753</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>757</v>
+      </c>
+      <c r="B111" t="s">
+        <v>758</v>
+      </c>
+      <c r="C111" t="s">
+        <v>583</v>
+      </c>
+      <c r="D111" t="s">
+        <v>246</v>
+      </c>
+      <c r="E111" t="s">
+        <v>759</v>
+      </c>
+      <c r="F111" t="s">
+        <v>760</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>757</v>
+      </c>
+      <c r="B112" t="s">
+        <v>758</v>
+      </c>
+      <c r="C112" t="s">
+        <v>587</v>
+      </c>
+      <c r="D112" t="s">
+        <v>246</v>
+      </c>
+      <c r="E112" t="s">
+        <v>759</v>
+      </c>
+      <c r="F112" t="s">
+        <v>760</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>763</v>
+      </c>
+      <c r="B113" t="s">
+        <v>764</v>
+      </c>
+      <c r="C113" t="s">
+        <v>47</v>
+      </c>
+      <c r="D113" t="s">
+        <v>246</v>
+      </c>
+      <c r="E113" t="s">
+        <v>765</v>
+      </c>
+      <c r="F113" t="s">
+        <v>766</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>768</v>
+      </c>
+      <c r="B114" t="s">
+        <v>769</v>
+      </c>
+      <c r="C114" t="s">
+        <v>770</v>
+      </c>
+      <c r="D114" t="s">
+        <v>246</v>
+      </c>
+      <c r="E114" t="s">
+        <v>676</v>
+      </c>
+      <c r="F114" t="s">
+        <v>771</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>773</v>
+      </c>
+      <c r="B115" t="s">
+        <v>774</v>
+      </c>
+      <c r="C115" t="s">
+        <v>360</v>
+      </c>
+      <c r="D115" t="s">
         <v>239</v>
       </c>
-      <c r="E82" t="s">
-        <v>624</v>
-      </c>
-      <c r="F82" t="s">
-        <v>625</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>626</v>
+      <c r="E115" t="s">
+        <v>268</v>
+      </c>
+      <c r="F115" t="s">
+        <v>303</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>776</v>
+      </c>
+      <c r="B116" t="s">
+        <v>777</v>
+      </c>
+      <c r="C116" t="s">
+        <v>360</v>
+      </c>
+      <c r="D116" t="s">
+        <v>246</v>
+      </c>
+      <c r="E116" t="s">
+        <v>778</v>
+      </c>
+      <c r="F116" t="s">
+        <v>779</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>781</v>
+      </c>
+      <c r="B117" t="s">
+        <v>782</v>
+      </c>
+      <c r="C117" t="s">
+        <v>654</v>
+      </c>
+      <c r="D117" t="s">
+        <v>246</v>
+      </c>
+      <c r="E117" t="s">
+        <v>783</v>
+      </c>
+      <c r="F117" t="s">
+        <v>784</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>786</v>
+      </c>
+      <c r="B118" t="s">
+        <v>787</v>
+      </c>
+      <c r="C118" t="s">
+        <v>654</v>
+      </c>
+      <c r="D118" t="s">
+        <v>246</v>
+      </c>
+      <c r="E118" t="s">
+        <v>542</v>
+      </c>
+      <c r="F118" t="s">
+        <v>320</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>789</v>
+      </c>
+      <c r="B119" t="s">
+        <v>435</v>
+      </c>
+      <c r="C119" t="s">
+        <v>790</v>
+      </c>
+      <c r="D119" t="s">
+        <v>379</v>
+      </c>
+      <c r="E119" t="s">
+        <v>791</v>
+      </c>
+      <c r="F119" t="s">
+        <v>268</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>793</v>
+      </c>
+      <c r="B120" t="s">
+        <v>794</v>
+      </c>
+      <c r="C120" t="s">
+        <v>360</v>
+      </c>
+      <c r="D120" t="s">
+        <v>246</v>
+      </c>
+      <c r="E120" t="s">
+        <v>627</v>
+      </c>
+      <c r="F120" t="s">
+        <v>268</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>796</v>
+      </c>
+      <c r="B121" t="s">
+        <v>797</v>
+      </c>
+      <c r="C121" t="s">
+        <v>798</v>
+      </c>
+      <c r="D121" t="s">
+        <v>246</v>
+      </c>
+      <c r="E121" t="s">
+        <v>799</v>
+      </c>
+      <c r="F121" t="s">
+        <v>387</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>801</v>
+      </c>
+      <c r="B122" t="s">
+        <v>769</v>
+      </c>
+      <c r="C122" t="s">
+        <v>770</v>
+      </c>
+      <c r="D122" t="s">
+        <v>246</v>
+      </c>
+      <c r="E122" t="s">
+        <v>802</v>
+      </c>
+      <c r="F122" t="s">
+        <v>803</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>805</v>
+      </c>
+      <c r="B123" t="s">
+        <v>806</v>
+      </c>
+      <c r="C123" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" t="s">
+        <v>246</v>
+      </c>
+      <c r="E123" t="s">
+        <v>807</v>
+      </c>
+      <c r="F123" t="s">
+        <v>808</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>810</v>
+      </c>
+      <c r="B124" t="s">
+        <v>811</v>
+      </c>
+      <c r="C124" t="s">
+        <v>396</v>
+      </c>
+      <c r="D124" t="s">
+        <v>246</v>
+      </c>
+      <c r="E124" t="s">
+        <v>812</v>
+      </c>
+      <c r="F124" t="s">
+        <v>813</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>815</v>
+      </c>
+      <c r="B125" t="s">
+        <v>816</v>
+      </c>
+      <c r="C125" t="s">
+        <v>817</v>
+      </c>
+      <c r="D125" t="s">
+        <v>246</v>
+      </c>
+      <c r="E125" t="s">
+        <v>818</v>
+      </c>
+      <c r="F125" t="s">
+        <v>819</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>821</v>
+      </c>
+      <c r="B126" t="s">
+        <v>822</v>
+      </c>
+      <c r="C126" t="s">
+        <v>823</v>
+      </c>
+      <c r="D126" t="s">
+        <v>246</v>
+      </c>
+      <c r="E126" t="s">
+        <v>824</v>
+      </c>
+      <c r="F126" t="s">
+        <v>825</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>827</v>
+      </c>
+      <c r="B127" t="s">
+        <v>526</v>
+      </c>
+      <c r="C127" t="s">
+        <v>307</v>
+      </c>
+      <c r="D127" t="s">
+        <v>246</v>
+      </c>
+      <c r="E127" t="s">
+        <v>828</v>
+      </c>
+      <c r="F127" t="s">
+        <v>637</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>830</v>
+      </c>
+      <c r="B128" t="s">
+        <v>831</v>
+      </c>
+      <c r="C128" t="s">
+        <v>832</v>
+      </c>
+      <c r="D128" t="s">
+        <v>379</v>
+      </c>
+      <c r="E128" t="s">
+        <v>833</v>
+      </c>
+      <c r="F128" t="s">
+        <v>834</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>830</v>
+      </c>
+      <c r="B129" t="s">
+        <v>836</v>
+      </c>
+      <c r="C129" t="s">
+        <v>278</v>
+      </c>
+      <c r="D129" t="s">
+        <v>246</v>
+      </c>
+      <c r="E129" t="s">
+        <v>338</v>
+      </c>
+      <c r="F129" t="s">
+        <v>615</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>830</v>
+      </c>
+      <c r="B130" t="s">
+        <v>838</v>
+      </c>
+      <c r="C130" t="s">
+        <v>288</v>
+      </c>
+      <c r="D130" t="s">
+        <v>246</v>
+      </c>
+      <c r="E130" t="s">
+        <v>839</v>
+      </c>
+      <c r="F130" t="s">
+        <v>840</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>830</v>
+      </c>
+      <c r="B131" t="s">
+        <v>842</v>
+      </c>
+      <c r="C131" t="s">
+        <v>843</v>
+      </c>
+      <c r="D131" t="s">
+        <v>246</v>
+      </c>
+      <c r="E131" t="s">
+        <v>844</v>
+      </c>
+      <c r="F131" t="s">
+        <v>845</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>830</v>
+      </c>
+      <c r="B132" t="s">
+        <v>842</v>
+      </c>
+      <c r="C132" t="s">
+        <v>847</v>
+      </c>
+      <c r="D132" t="s">
+        <v>246</v>
+      </c>
+      <c r="E132" t="s">
+        <v>844</v>
+      </c>
+      <c r="F132" t="s">
+        <v>845</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>830</v>
+      </c>
+      <c r="B133" t="s">
+        <v>842</v>
+      </c>
+      <c r="C133" t="s">
+        <v>296</v>
+      </c>
+      <c r="D133" t="s">
+        <v>246</v>
+      </c>
+      <c r="E133" t="s">
+        <v>844</v>
+      </c>
+      <c r="F133" t="s">
+        <v>845</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>850</v>
+      </c>
+      <c r="B134" t="s">
+        <v>851</v>
+      </c>
+      <c r="C134" t="s">
+        <v>852</v>
+      </c>
+      <c r="D134" t="s">
+        <v>246</v>
+      </c>
+      <c r="E134" t="s">
+        <v>853</v>
+      </c>
+      <c r="F134" t="s">
+        <v>854</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>856</v>
+      </c>
+      <c r="B135" t="s">
+        <v>851</v>
+      </c>
+      <c r="C135" t="s">
+        <v>278</v>
+      </c>
+      <c r="D135" t="s">
+        <v>246</v>
+      </c>
+      <c r="E135" t="s">
+        <v>853</v>
+      </c>
+      <c r="F135" t="s">
+        <v>854</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>858</v>
+      </c>
+      <c r="B136" t="s">
+        <v>859</v>
+      </c>
+      <c r="C136" t="s">
+        <v>360</v>
+      </c>
+      <c r="D136" t="s">
+        <v>246</v>
+      </c>
+      <c r="E136" t="s">
+        <v>860</v>
+      </c>
+      <c r="F136" t="s">
+        <v>241</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>862</v>
+      </c>
+      <c r="B137" t="s">
+        <v>863</v>
+      </c>
+      <c r="C137" t="s">
+        <v>864</v>
+      </c>
+      <c r="D137" t="s">
+        <v>379</v>
+      </c>
+      <c r="E137" t="s">
+        <v>268</v>
+      </c>
+      <c r="F137" t="s">
+        <v>865</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>867</v>
+      </c>
+      <c r="B138" t="s">
+        <v>868</v>
+      </c>
+      <c r="C138" t="s">
+        <v>288</v>
+      </c>
+      <c r="D138" t="s">
+        <v>246</v>
+      </c>
+      <c r="E138" t="s">
+        <v>869</v>
+      </c>
+      <c r="F138" t="s">
+        <v>339</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>871</v>
+      </c>
+      <c r="B139" t="s">
+        <v>640</v>
+      </c>
+      <c r="C139" t="s">
+        <v>278</v>
+      </c>
+      <c r="D139" t="s">
+        <v>246</v>
+      </c>
+      <c r="E139" t="s">
+        <v>872</v>
+      </c>
+      <c r="F139" t="s">
+        <v>873</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>875</v>
+      </c>
+      <c r="B140" t="s">
+        <v>876</v>
+      </c>
+      <c r="C140" t="s">
+        <v>877</v>
+      </c>
+      <c r="D140" t="s">
+        <v>246</v>
+      </c>
+      <c r="E140" t="s">
+        <v>878</v>
+      </c>
+      <c r="F140" t="s">
+        <v>268</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>880</v>
+      </c>
+      <c r="B141" t="s">
+        <v>881</v>
+      </c>
+      <c r="C141" t="s">
+        <v>882</v>
+      </c>
+      <c r="D141" t="s">
+        <v>246</v>
+      </c>
+      <c r="E141" t="s">
+        <v>883</v>
+      </c>
+      <c r="F141" t="s">
+        <v>884</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>886</v>
+      </c>
+      <c r="B142" t="s">
+        <v>887</v>
+      </c>
+      <c r="C142" t="s">
+        <v>888</v>
+      </c>
+      <c r="D142" t="s">
+        <v>246</v>
+      </c>
+      <c r="E142" t="s">
+        <v>889</v>
+      </c>
+      <c r="F142" t="s">
+        <v>890</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>892</v>
+      </c>
+      <c r="B143" t="s">
+        <v>893</v>
+      </c>
+      <c r="C143" t="s">
+        <v>894</v>
+      </c>
+      <c r="D143" t="s">
+        <v>246</v>
+      </c>
+      <c r="E143" t="s">
+        <v>676</v>
+      </c>
+      <c r="F143" t="s">
+        <v>895</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>897</v>
+      </c>
+      <c r="B144" t="s">
+        <v>576</v>
+      </c>
+      <c r="C144" t="s">
+        <v>577</v>
+      </c>
+      <c r="D144" t="s">
+        <v>246</v>
+      </c>
+      <c r="E144" t="s">
+        <v>898</v>
+      </c>
+      <c r="F144" t="s">
+        <v>899</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -5492,6 +7740,68 @@
     <hyperlink ref="H80" r:id="rId79"/>
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-16.xlsx
+++ b/docs/xlsx/jobs-2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="903">
   <si>
     <t>Title</t>
   </si>
@@ -1798,16 +1798,22 @@
     <t>https://www.idealist.org/en/nonprofit-job/6fea478b5d8b44fcb48f132cd1422808-internal-and-external-union-organizers-service-employees-international-union-local-925-seattle-seattle</t>
   </si>
   <si>
+    <t>Large Scale Partnerships Manager</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>USD 5000.00 - 5000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/180ed5a6188a4a3dbf66502f9c682931-large-scale-partnerships-manager-rescuing-leftover-cuisine-new-york</t>
+  </si>
+  <si>
     <t>Large Scale Partnerships Manager (Wonder Grant)</t>
-  </si>
-  <si>
-    <t>Rescuing Leftover Cuisine</t>
-  </si>
-  <si>
-    <t>USD 5000.00 - 5000.00/month</t>
-  </si>
-  <si>
-    <t>Community Development, Housing Homelessness, Philanthropy</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/180ed5a6188a4a3dbf66502f9c682931-large-scale-partnerships-manager-wonder-grant-rescuing-leftover-cuisine-new-york</t>
@@ -4328,7 +4334,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -6051,134 +6057,134 @@
         <v>599</v>
       </c>
       <c r="B75" t="s">
+        <v>595</v>
+      </c>
+      <c r="C75" t="s">
+        <v>278</v>
+      </c>
+      <c r="D75" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" t="s">
+        <v>596</v>
+      </c>
+      <c r="F75" t="s">
+        <v>597</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="C75" t="s">
-        <v>360</v>
-      </c>
-      <c r="D75" t="s">
-        <v>246</v>
-      </c>
-      <c r="E75" t="s">
-        <v>601</v>
-      </c>
-      <c r="F75" t="s">
-        <v>602</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>601</v>
+      </c>
+      <c r="B76" t="s">
+        <v>602</v>
+      </c>
+      <c r="C76" t="s">
+        <v>360</v>
+      </c>
+      <c r="D76" t="s">
+        <v>246</v>
+      </c>
+      <c r="E76" t="s">
+        <v>603</v>
+      </c>
+      <c r="F76" t="s">
         <v>604</v>
       </c>
-      <c r="B76" t="s">
+      <c r="H76" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="C76" t="s">
-        <v>278</v>
-      </c>
-      <c r="D76" t="s">
-        <v>246</v>
-      </c>
-      <c r="E76" t="s">
-        <v>606</v>
-      </c>
-      <c r="F76" t="s">
-        <v>607</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>606</v>
+      </c>
+      <c r="B77" t="s">
+        <v>607</v>
+      </c>
+      <c r="C77" t="s">
+        <v>278</v>
+      </c>
+      <c r="D77" t="s">
+        <v>246</v>
+      </c>
+      <c r="E77" t="s">
+        <v>608</v>
+      </c>
+      <c r="F77" t="s">
         <v>609</v>
       </c>
-      <c r="B77" t="s">
-        <v>342</v>
-      </c>
-      <c r="C77" t="s">
-        <v>343</v>
-      </c>
-      <c r="D77" t="s">
-        <v>246</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="H77" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="F77" t="s">
-        <v>345</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>611</v>
+      </c>
+      <c r="B78" t="s">
+        <v>342</v>
+      </c>
+      <c r="C78" t="s">
+        <v>343</v>
+      </c>
+      <c r="D78" t="s">
+        <v>246</v>
+      </c>
+      <c r="E78" t="s">
         <v>612</v>
       </c>
-      <c r="B78" t="s">
+      <c r="F78" t="s">
+        <v>345</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="C78" t="s">
-        <v>278</v>
-      </c>
-      <c r="D78" t="s">
-        <v>246</v>
-      </c>
-      <c r="E78" t="s">
-        <v>614</v>
-      </c>
-      <c r="F78" t="s">
-        <v>615</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>614</v>
+      </c>
+      <c r="B79" t="s">
+        <v>615</v>
+      </c>
+      <c r="C79" t="s">
+        <v>278</v>
+      </c>
+      <c r="D79" t="s">
+        <v>246</v>
+      </c>
+      <c r="E79" t="s">
+        <v>616</v>
+      </c>
+      <c r="F79" t="s">
         <v>617</v>
       </c>
-      <c r="B79" t="s">
+      <c r="H79" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="C79" t="s">
-        <v>288</v>
-      </c>
-      <c r="D79" t="s">
-        <v>246</v>
-      </c>
-      <c r="E79" t="s">
-        <v>619</v>
-      </c>
-      <c r="F79" t="s">
-        <v>620</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>619</v>
+      </c>
+      <c r="B80" t="s">
+        <v>620</v>
+      </c>
+      <c r="C80" t="s">
+        <v>288</v>
+      </c>
+      <c r="D80" t="s">
+        <v>246</v>
+      </c>
+      <c r="E80" t="s">
+        <v>621</v>
+      </c>
+      <c r="F80" t="s">
         <v>622</v>
-      </c>
-      <c r="B80" t="s">
-        <v>613</v>
-      </c>
-      <c r="C80" t="s">
-        <v>278</v>
-      </c>
-      <c r="D80" t="s">
-        <v>246</v>
-      </c>
-      <c r="E80" t="s">
-        <v>614</v>
-      </c>
-      <c r="F80" t="s">
-        <v>615</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>623</v>
@@ -6189,214 +6195,214 @@
         <v>624</v>
       </c>
       <c r="B81" t="s">
+        <v>615</v>
+      </c>
+      <c r="C81" t="s">
+        <v>278</v>
+      </c>
+      <c r="D81" t="s">
+        <v>246</v>
+      </c>
+      <c r="E81" t="s">
+        <v>616</v>
+      </c>
+      <c r="F81" t="s">
+        <v>617</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="C81" t="s">
-        <v>626</v>
-      </c>
-      <c r="D81" t="s">
-        <v>246</v>
-      </c>
-      <c r="E81" t="s">
-        <v>627</v>
-      </c>
-      <c r="F81" t="s">
-        <v>628</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>626</v>
+      </c>
+      <c r="B82" t="s">
+        <v>627</v>
+      </c>
+      <c r="C82" t="s">
+        <v>628</v>
+      </c>
+      <c r="D82" t="s">
+        <v>246</v>
+      </c>
+      <c r="E82" t="s">
+        <v>629</v>
+      </c>
+      <c r="F82" t="s">
         <v>630</v>
       </c>
-      <c r="B82" t="s">
+      <c r="H82" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="C82" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" t="s">
-        <v>246</v>
-      </c>
-      <c r="E82" t="s">
-        <v>632</v>
-      </c>
-      <c r="F82" t="s">
-        <v>633</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>632</v>
+      </c>
+      <c r="B83" t="s">
+        <v>633</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>246</v>
+      </c>
+      <c r="E83" t="s">
+        <v>634</v>
+      </c>
+      <c r="F83" t="s">
         <v>635</v>
       </c>
-      <c r="B83" t="s">
-        <v>526</v>
-      </c>
-      <c r="C83" t="s">
-        <v>307</v>
-      </c>
-      <c r="D83" t="s">
-        <v>246</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="H83" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="F83" t="s">
-        <v>637</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>637</v>
+      </c>
+      <c r="B84" t="s">
+        <v>526</v>
+      </c>
+      <c r="C84" t="s">
+        <v>307</v>
+      </c>
+      <c r="D84" t="s">
+        <v>246</v>
+      </c>
+      <c r="E84" t="s">
+        <v>638</v>
+      </c>
+      <c r="F84" t="s">
         <v>639</v>
       </c>
-      <c r="B84" t="s">
+      <c r="H84" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="C84" t="s">
-        <v>278</v>
-      </c>
-      <c r="D84" t="s">
-        <v>246</v>
-      </c>
-      <c r="E84" t="s">
-        <v>641</v>
-      </c>
-      <c r="F84" t="s">
-        <v>642</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>641</v>
+      </c>
+      <c r="B85" t="s">
+        <v>642</v>
+      </c>
+      <c r="C85" t="s">
+        <v>278</v>
+      </c>
+      <c r="D85" t="s">
+        <v>246</v>
+      </c>
+      <c r="E85" t="s">
+        <v>643</v>
+      </c>
+      <c r="F85" t="s">
         <v>644</v>
       </c>
-      <c r="B85" t="s">
-        <v>526</v>
-      </c>
-      <c r="C85" t="s">
-        <v>307</v>
-      </c>
-      <c r="D85" t="s">
-        <v>246</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="H85" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="F85" t="s">
-        <v>646</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>646</v>
+      </c>
+      <c r="B86" t="s">
+        <v>526</v>
+      </c>
+      <c r="C86" t="s">
+        <v>307</v>
+      </c>
+      <c r="D86" t="s">
+        <v>246</v>
+      </c>
+      <c r="E86" t="s">
+        <v>647</v>
+      </c>
+      <c r="F86" t="s">
         <v>648</v>
       </c>
-      <c r="B86" t="s">
+      <c r="H86" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="C86" t="s">
-        <v>360</v>
-      </c>
-      <c r="D86" t="s">
-        <v>246</v>
-      </c>
-      <c r="E86" t="s">
-        <v>422</v>
-      </c>
-      <c r="F86" t="s">
-        <v>650</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>650</v>
+      </c>
+      <c r="B87" t="s">
+        <v>651</v>
+      </c>
+      <c r="C87" t="s">
+        <v>360</v>
+      </c>
+      <c r="D87" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" t="s">
+        <v>422</v>
+      </c>
+      <c r="F87" t="s">
         <v>652</v>
       </c>
-      <c r="B87" t="s">
+      <c r="H87" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="C87" t="s">
-        <v>654</v>
-      </c>
-      <c r="D87" t="s">
-        <v>246</v>
-      </c>
-      <c r="E87" t="s">
-        <v>655</v>
-      </c>
-      <c r="F87" t="s">
-        <v>656</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>654</v>
+      </c>
+      <c r="B88" t="s">
+        <v>655</v>
+      </c>
+      <c r="C88" t="s">
+        <v>656</v>
+      </c>
+      <c r="D88" t="s">
+        <v>246</v>
+      </c>
+      <c r="E88" t="s">
+        <v>657</v>
+      </c>
+      <c r="F88" t="s">
         <v>658</v>
       </c>
-      <c r="B88" t="s">
+      <c r="H88" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="C88" t="s">
-        <v>360</v>
-      </c>
-      <c r="D88" t="s">
-        <v>253</v>
-      </c>
-      <c r="E88" t="s">
-        <v>660</v>
-      </c>
-      <c r="F88" t="s">
-        <v>661</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B89" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C89" t="s">
         <v>360</v>
       </c>
       <c r="D89" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E89" t="s">
+        <v>662</v>
+      </c>
+      <c r="F89" t="s">
+        <v>663</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="F89" t="s">
-        <v>661</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B90" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C90" t="s">
         <v>360</v>
@@ -6405,21 +6411,21 @@
         <v>246</v>
       </c>
       <c r="E90" t="s">
+        <v>666</v>
+      </c>
+      <c r="F90" t="s">
+        <v>663</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="F90" t="s">
-        <v>661</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B91" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C91" t="s">
         <v>360</v>
@@ -6428,10 +6434,10 @@
         <v>246</v>
       </c>
       <c r="E91" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F91" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>670</v>
@@ -6442,433 +6448,433 @@
         <v>671</v>
       </c>
       <c r="B92" t="s">
+        <v>661</v>
+      </c>
+      <c r="C92" t="s">
+        <v>360</v>
+      </c>
+      <c r="D92" t="s">
+        <v>246</v>
+      </c>
+      <c r="E92" t="s">
+        <v>669</v>
+      </c>
+      <c r="F92" t="s">
+        <v>663</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C92" t="s">
-        <v>307</v>
-      </c>
-      <c r="D92" t="s">
-        <v>379</v>
-      </c>
-      <c r="E92" t="s">
-        <v>660</v>
-      </c>
-      <c r="F92" t="s">
-        <v>673</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B93" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C93" t="s">
         <v>307</v>
       </c>
       <c r="D93" t="s">
-        <v>246</v>
+        <v>379</v>
       </c>
       <c r="E93" t="s">
+        <v>662</v>
+      </c>
+      <c r="F93" t="s">
+        <v>675</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="F93" t="s">
-        <v>677</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>677</v>
+      </c>
+      <c r="B94" t="s">
+        <v>674</v>
+      </c>
+      <c r="C94" t="s">
+        <v>307</v>
+      </c>
+      <c r="D94" t="s">
+        <v>246</v>
+      </c>
+      <c r="E94" t="s">
+        <v>678</v>
+      </c>
+      <c r="F94" t="s">
         <v>679</v>
       </c>
-      <c r="B94" t="s">
+      <c r="H94" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="C94" t="s">
-        <v>278</v>
-      </c>
-      <c r="D94" t="s">
-        <v>253</v>
-      </c>
-      <c r="E94" t="s">
-        <v>681</v>
-      </c>
-      <c r="F94" t="s">
-        <v>682</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>133</v>
+        <v>681</v>
       </c>
       <c r="B95" t="s">
+        <v>682</v>
+      </c>
+      <c r="C95" t="s">
+        <v>278</v>
+      </c>
+      <c r="D95" t="s">
+        <v>253</v>
+      </c>
+      <c r="E95" t="s">
+        <v>683</v>
+      </c>
+      <c r="F95" t="s">
         <v>684</v>
       </c>
-      <c r="C95" t="s">
-        <v>360</v>
-      </c>
-      <c r="D95" t="s">
-        <v>246</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="H95" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="F95" t="s">
-        <v>268</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>133</v>
+      </c>
+      <c r="B96" t="s">
+        <v>686</v>
+      </c>
+      <c r="C96" t="s">
+        <v>360</v>
+      </c>
+      <c r="D96" t="s">
+        <v>246</v>
+      </c>
+      <c r="E96" t="s">
         <v>687</v>
       </c>
-      <c r="B96" t="s">
-        <v>489</v>
-      </c>
-      <c r="C96" t="s">
-        <v>288</v>
-      </c>
-      <c r="D96" t="s">
-        <v>246</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>268</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="F96" t="s">
-        <v>491</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>689</v>
+      </c>
+      <c r="B97" t="s">
+        <v>489</v>
+      </c>
+      <c r="C97" t="s">
+        <v>288</v>
+      </c>
+      <c r="D97" t="s">
+        <v>246</v>
+      </c>
+      <c r="E97" t="s">
         <v>690</v>
       </c>
-      <c r="B97" t="s">
+      <c r="F97" t="s">
+        <v>491</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="C97" t="s">
-        <v>692</v>
-      </c>
-      <c r="D97" t="s">
-        <v>379</v>
-      </c>
-      <c r="E97" t="s">
-        <v>693</v>
-      </c>
-      <c r="F97" t="s">
-        <v>694</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>692</v>
+      </c>
+      <c r="B98" t="s">
+        <v>693</v>
+      </c>
+      <c r="C98" t="s">
+        <v>694</v>
+      </c>
+      <c r="D98" t="s">
+        <v>379</v>
+      </c>
+      <c r="E98" t="s">
+        <v>695</v>
+      </c>
+      <c r="F98" t="s">
         <v>696</v>
       </c>
-      <c r="B98" t="s">
+      <c r="H98" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="C98" t="s">
-        <v>692</v>
-      </c>
-      <c r="D98" t="s">
-        <v>246</v>
-      </c>
-      <c r="E98" t="s">
-        <v>641</v>
-      </c>
-      <c r="F98" t="s">
-        <v>698</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>698</v>
+      </c>
+      <c r="B99" t="s">
+        <v>699</v>
+      </c>
+      <c r="C99" t="s">
+        <v>694</v>
+      </c>
+      <c r="D99" t="s">
+        <v>246</v>
+      </c>
+      <c r="E99" t="s">
+        <v>643</v>
+      </c>
+      <c r="F99" t="s">
         <v>700</v>
       </c>
-      <c r="B99" t="s">
+      <c r="H99" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C99" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" t="s">
-        <v>246</v>
-      </c>
-      <c r="E99" t="s">
-        <v>702</v>
-      </c>
-      <c r="F99" t="s">
-        <v>703</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>702</v>
+      </c>
+      <c r="B100" t="s">
+        <v>703</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" t="s">
+        <v>246</v>
+      </c>
+      <c r="E100" t="s">
+        <v>704</v>
+      </c>
+      <c r="F100" t="s">
         <v>705</v>
       </c>
-      <c r="B100" t="s">
+      <c r="H100" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="C100" t="s">
-        <v>278</v>
-      </c>
-      <c r="D100" t="s">
-        <v>707</v>
-      </c>
-      <c r="E100" t="s">
-        <v>708</v>
-      </c>
-      <c r="F100" t="s">
-        <v>709</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>707</v>
+      </c>
+      <c r="B101" t="s">
+        <v>708</v>
+      </c>
+      <c r="C101" t="s">
+        <v>278</v>
+      </c>
+      <c r="D101" t="s">
+        <v>709</v>
+      </c>
+      <c r="E101" t="s">
+        <v>710</v>
+      </c>
+      <c r="F101" t="s">
         <v>711</v>
       </c>
-      <c r="B101" t="s">
+      <c r="H101" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="C101" t="s">
-        <v>396</v>
-      </c>
-      <c r="D101" t="s">
-        <v>253</v>
-      </c>
-      <c r="E101" t="s">
-        <v>268</v>
-      </c>
-      <c r="F101" t="s">
-        <v>713</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B102" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C102" t="s">
-        <v>692</v>
+        <v>396</v>
       </c>
       <c r="D102" t="s">
         <v>253</v>
       </c>
       <c r="E102" t="s">
-        <v>717</v>
+        <v>268</v>
       </c>
       <c r="F102" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>717</v>
+      </c>
+      <c r="B103" t="s">
+        <v>718</v>
+      </c>
+      <c r="C103" t="s">
+        <v>694</v>
+      </c>
+      <c r="D103" t="s">
+        <v>253</v>
+      </c>
+      <c r="E103" t="s">
+        <v>719</v>
+      </c>
+      <c r="F103" t="s">
         <v>720</v>
       </c>
-      <c r="B103" t="s">
+      <c r="H103" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="C103" t="s">
-        <v>722</v>
-      </c>
-      <c r="D103" t="s">
-        <v>246</v>
-      </c>
-      <c r="E103" t="s">
-        <v>723</v>
-      </c>
-      <c r="F103" t="s">
-        <v>724</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>144</v>
+        <v>722</v>
       </c>
       <c r="B104" t="s">
+        <v>723</v>
+      </c>
+      <c r="C104" t="s">
+        <v>724</v>
+      </c>
+      <c r="D104" t="s">
+        <v>246</v>
+      </c>
+      <c r="E104" t="s">
+        <v>725</v>
+      </c>
+      <c r="F104" t="s">
         <v>726</v>
       </c>
-      <c r="C104" t="s">
+      <c r="H104" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D104" t="s">
-        <v>246</v>
-      </c>
-      <c r="E104" t="s">
-        <v>268</v>
-      </c>
-      <c r="F104" t="s">
-        <v>728</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>144</v>
+      </c>
+      <c r="B105" t="s">
+        <v>728</v>
+      </c>
+      <c r="C105" t="s">
+        <v>729</v>
+      </c>
+      <c r="D105" t="s">
+        <v>246</v>
+      </c>
+      <c r="E105" t="s">
+        <v>268</v>
+      </c>
+      <c r="F105" t="s">
         <v>730</v>
       </c>
-      <c r="B105" t="s">
+      <c r="H105" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="C105" t="s">
-        <v>366</v>
-      </c>
-      <c r="D105" t="s">
-        <v>707</v>
-      </c>
-      <c r="E105" t="s">
-        <v>732</v>
-      </c>
-      <c r="F105" t="s">
-        <v>733</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>732</v>
+      </c>
+      <c r="B106" t="s">
+        <v>733</v>
+      </c>
+      <c r="C106" t="s">
+        <v>366</v>
+      </c>
+      <c r="D106" t="s">
+        <v>709</v>
+      </c>
+      <c r="E106" t="s">
+        <v>734</v>
+      </c>
+      <c r="F106" t="s">
         <v>735</v>
       </c>
-      <c r="B106" t="s">
+      <c r="H106" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="C106" t="s">
-        <v>737</v>
-      </c>
-      <c r="D106" t="s">
-        <v>246</v>
-      </c>
-      <c r="E106" t="s">
-        <v>268</v>
-      </c>
-      <c r="F106" t="s">
-        <v>268</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>737</v>
+      </c>
+      <c r="B107" t="s">
+        <v>738</v>
+      </c>
+      <c r="C107" t="s">
         <v>739</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
+        <v>246</v>
+      </c>
+      <c r="E107" t="s">
+        <v>268</v>
+      </c>
+      <c r="F107" t="s">
+        <v>268</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="C107" t="s">
-        <v>741</v>
-      </c>
-      <c r="D107" t="s">
-        <v>246</v>
-      </c>
-      <c r="E107" t="s">
-        <v>742</v>
-      </c>
-      <c r="F107" t="s">
-        <v>743</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>741</v>
+      </c>
+      <c r="B108" t="s">
+        <v>742</v>
+      </c>
+      <c r="C108" t="s">
+        <v>743</v>
+      </c>
+      <c r="D108" t="s">
+        <v>246</v>
+      </c>
+      <c r="E108" t="s">
+        <v>744</v>
+      </c>
+      <c r="F108" t="s">
         <v>745</v>
       </c>
-      <c r="B108" t="s">
+      <c r="H108" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="C108" t="s">
-        <v>278</v>
-      </c>
-      <c r="D108" t="s">
-        <v>246</v>
-      </c>
-      <c r="E108" t="s">
-        <v>747</v>
-      </c>
-      <c r="F108" t="s">
-        <v>748</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>747</v>
+      </c>
+      <c r="B109" t="s">
+        <v>748</v>
+      </c>
+      <c r="C109" t="s">
+        <v>278</v>
+      </c>
+      <c r="D109" t="s">
+        <v>246</v>
+      </c>
+      <c r="E109" t="s">
+        <v>749</v>
+      </c>
+      <c r="F109" t="s">
         <v>750</v>
       </c>
-      <c r="B109" t="s">
+      <c r="H109" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="C109" t="s">
-        <v>307</v>
-      </c>
-      <c r="D109" t="s">
-        <v>246</v>
-      </c>
-      <c r="E109" t="s">
-        <v>752</v>
-      </c>
-      <c r="F109" t="s">
-        <v>753</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B110" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C110" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="D110" t="s">
         <v>246</v>
       </c>
       <c r="E110" t="s">
+        <v>754</v>
+      </c>
+      <c r="F110" t="s">
         <v>755</v>
-      </c>
-      <c r="F110" t="s">
-        <v>753</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>756</v>
@@ -6876,436 +6882,436 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>752</v>
+      </c>
+      <c r="B111" t="s">
+        <v>753</v>
+      </c>
+      <c r="C111" t="s">
+        <v>278</v>
+      </c>
+      <c r="D111" t="s">
+        <v>246</v>
+      </c>
+      <c r="E111" t="s">
         <v>757</v>
       </c>
-      <c r="B111" t="s">
+      <c r="F111" t="s">
+        <v>755</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="C111" t="s">
-        <v>583</v>
-      </c>
-      <c r="D111" t="s">
-        <v>246</v>
-      </c>
-      <c r="E111" t="s">
-        <v>759</v>
-      </c>
-      <c r="F111" t="s">
-        <v>760</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B112" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C112" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D112" t="s">
         <v>246</v>
       </c>
       <c r="E112" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="F112" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B113" t="s">
+        <v>760</v>
+      </c>
+      <c r="C113" t="s">
+        <v>587</v>
+      </c>
+      <c r="D113" t="s">
+        <v>246</v>
+      </c>
+      <c r="E113" t="s">
+        <v>761</v>
+      </c>
+      <c r="F113" t="s">
+        <v>762</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="C113" t="s">
-        <v>47</v>
-      </c>
-      <c r="D113" t="s">
-        <v>246</v>
-      </c>
-      <c r="E113" t="s">
-        <v>765</v>
-      </c>
-      <c r="F113" t="s">
-        <v>766</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>765</v>
+      </c>
+      <c r="B114" t="s">
+        <v>766</v>
+      </c>
+      <c r="C114" t="s">
+        <v>47</v>
+      </c>
+      <c r="D114" t="s">
+        <v>246</v>
+      </c>
+      <c r="E114" t="s">
+        <v>767</v>
+      </c>
+      <c r="F114" t="s">
         <v>768</v>
       </c>
-      <c r="B114" t="s">
+      <c r="H114" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="C114" t="s">
-        <v>770</v>
-      </c>
-      <c r="D114" t="s">
-        <v>246</v>
-      </c>
-      <c r="E114" t="s">
-        <v>676</v>
-      </c>
-      <c r="F114" t="s">
-        <v>771</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>770</v>
+      </c>
+      <c r="B115" t="s">
+        <v>771</v>
+      </c>
+      <c r="C115" t="s">
+        <v>772</v>
+      </c>
+      <c r="D115" t="s">
+        <v>246</v>
+      </c>
+      <c r="E115" t="s">
+        <v>678</v>
+      </c>
+      <c r="F115" t="s">
         <v>773</v>
       </c>
-      <c r="B115" t="s">
+      <c r="H115" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C115" t="s">
-        <v>360</v>
-      </c>
-      <c r="D115" t="s">
-        <v>239</v>
-      </c>
-      <c r="E115" t="s">
-        <v>268</v>
-      </c>
-      <c r="F115" t="s">
-        <v>303</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>775</v>
+      </c>
+      <c r="B116" t="s">
         <v>776</v>
-      </c>
-      <c r="B116" t="s">
-        <v>777</v>
       </c>
       <c r="C116" t="s">
         <v>360</v>
       </c>
       <c r="D116" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E116" t="s">
-        <v>778</v>
+        <v>268</v>
       </c>
       <c r="F116" t="s">
-        <v>779</v>
+        <v>303</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>778</v>
+      </c>
+      <c r="B117" t="s">
+        <v>779</v>
+      </c>
+      <c r="C117" t="s">
+        <v>360</v>
+      </c>
+      <c r="D117" t="s">
+        <v>246</v>
+      </c>
+      <c r="E117" t="s">
+        <v>780</v>
+      </c>
+      <c r="F117" t="s">
         <v>781</v>
       </c>
-      <c r="B117" t="s">
+      <c r="H117" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="C117" t="s">
-        <v>654</v>
-      </c>
-      <c r="D117" t="s">
-        <v>246</v>
-      </c>
-      <c r="E117" t="s">
-        <v>783</v>
-      </c>
-      <c r="F117" t="s">
-        <v>784</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>783</v>
+      </c>
+      <c r="B118" t="s">
+        <v>784</v>
+      </c>
+      <c r="C118" t="s">
+        <v>656</v>
+      </c>
+      <c r="D118" t="s">
+        <v>246</v>
+      </c>
+      <c r="E118" t="s">
+        <v>785</v>
+      </c>
+      <c r="F118" t="s">
         <v>786</v>
       </c>
-      <c r="B118" t="s">
+      <c r="H118" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="C118" t="s">
-        <v>654</v>
-      </c>
-      <c r="D118" t="s">
-        <v>246</v>
-      </c>
-      <c r="E118" t="s">
-        <v>542</v>
-      </c>
-      <c r="F118" t="s">
-        <v>320</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>788</v>
+      </c>
+      <c r="B119" t="s">
         <v>789</v>
       </c>
-      <c r="B119" t="s">
-        <v>435</v>
-      </c>
       <c r="C119" t="s">
+        <v>656</v>
+      </c>
+      <c r="D119" t="s">
+        <v>246</v>
+      </c>
+      <c r="E119" t="s">
+        <v>542</v>
+      </c>
+      <c r="F119" t="s">
+        <v>320</v>
+      </c>
+      <c r="H119" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D119" t="s">
-        <v>379</v>
-      </c>
-      <c r="E119" t="s">
-        <v>791</v>
-      </c>
-      <c r="F119" t="s">
-        <v>268</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>791</v>
+      </c>
+      <c r="B120" t="s">
+        <v>435</v>
+      </c>
+      <c r="C120" t="s">
+        <v>792</v>
+      </c>
+      <c r="D120" t="s">
+        <v>379</v>
+      </c>
+      <c r="E120" t="s">
         <v>793</v>
-      </c>
-      <c r="B120" t="s">
-        <v>794</v>
-      </c>
-      <c r="C120" t="s">
-        <v>360</v>
-      </c>
-      <c r="D120" t="s">
-        <v>246</v>
-      </c>
-      <c r="E120" t="s">
-        <v>627</v>
       </c>
       <c r="F120" t="s">
         <v>268</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>795</v>
+      </c>
+      <c r="B121" t="s">
         <v>796</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
+        <v>360</v>
+      </c>
+      <c r="D121" t="s">
+        <v>246</v>
+      </c>
+      <c r="E121" t="s">
+        <v>629</v>
+      </c>
+      <c r="F121" t="s">
+        <v>268</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="C121" t="s">
-        <v>798</v>
-      </c>
-      <c r="D121" t="s">
-        <v>246</v>
-      </c>
-      <c r="E121" t="s">
-        <v>799</v>
-      </c>
-      <c r="F121" t="s">
-        <v>387</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>798</v>
+      </c>
+      <c r="B122" t="s">
+        <v>799</v>
+      </c>
+      <c r="C122" t="s">
+        <v>800</v>
+      </c>
+      <c r="D122" t="s">
+        <v>246</v>
+      </c>
+      <c r="E122" t="s">
         <v>801</v>
       </c>
-      <c r="B122" t="s">
-        <v>769</v>
-      </c>
-      <c r="C122" t="s">
-        <v>770</v>
-      </c>
-      <c r="D122" t="s">
-        <v>246</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
+        <v>387</v>
+      </c>
+      <c r="H122" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="F122" t="s">
-        <v>803</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>803</v>
+      </c>
+      <c r="B123" t="s">
+        <v>771</v>
+      </c>
+      <c r="C123" t="s">
+        <v>772</v>
+      </c>
+      <c r="D123" t="s">
+        <v>246</v>
+      </c>
+      <c r="E123" t="s">
+        <v>804</v>
+      </c>
+      <c r="F123" t="s">
         <v>805</v>
       </c>
-      <c r="B123" t="s">
+      <c r="H123" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="C123" t="s">
-        <v>10</v>
-      </c>
-      <c r="D123" t="s">
-        <v>246</v>
-      </c>
-      <c r="E123" t="s">
-        <v>807</v>
-      </c>
-      <c r="F123" t="s">
-        <v>808</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>807</v>
+      </c>
+      <c r="B124" t="s">
+        <v>808</v>
+      </c>
+      <c r="C124" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" t="s">
+        <v>246</v>
+      </c>
+      <c r="E124" t="s">
+        <v>809</v>
+      </c>
+      <c r="F124" t="s">
         <v>810</v>
       </c>
-      <c r="B124" t="s">
+      <c r="H124" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="C124" t="s">
-        <v>396</v>
-      </c>
-      <c r="D124" t="s">
-        <v>246</v>
-      </c>
-      <c r="E124" t="s">
-        <v>812</v>
-      </c>
-      <c r="F124" t="s">
-        <v>813</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>812</v>
+      </c>
+      <c r="B125" t="s">
+        <v>813</v>
+      </c>
+      <c r="C125" t="s">
+        <v>396</v>
+      </c>
+      <c r="D125" t="s">
+        <v>246</v>
+      </c>
+      <c r="E125" t="s">
+        <v>814</v>
+      </c>
+      <c r="F125" t="s">
         <v>815</v>
       </c>
-      <c r="B125" t="s">
+      <c r="H125" s="2" t="s">
         <v>816</v>
-      </c>
-      <c r="C125" t="s">
-        <v>817</v>
-      </c>
-      <c r="D125" t="s">
-        <v>246</v>
-      </c>
-      <c r="E125" t="s">
-        <v>818</v>
-      </c>
-      <c r="F125" t="s">
-        <v>819</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>817</v>
+      </c>
+      <c r="B126" t="s">
+        <v>818</v>
+      </c>
+      <c r="C126" t="s">
+        <v>819</v>
+      </c>
+      <c r="D126" t="s">
+        <v>246</v>
+      </c>
+      <c r="E126" t="s">
+        <v>820</v>
+      </c>
+      <c r="F126" t="s">
         <v>821</v>
       </c>
-      <c r="B126" t="s">
+      <c r="H126" s="2" t="s">
         <v>822</v>
-      </c>
-      <c r="C126" t="s">
-        <v>823</v>
-      </c>
-      <c r="D126" t="s">
-        <v>246</v>
-      </c>
-      <c r="E126" t="s">
-        <v>824</v>
-      </c>
-      <c r="F126" t="s">
-        <v>825</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>823</v>
+      </c>
+      <c r="B127" t="s">
+        <v>824</v>
+      </c>
+      <c r="C127" t="s">
+        <v>825</v>
+      </c>
+      <c r="D127" t="s">
+        <v>246</v>
+      </c>
+      <c r="E127" t="s">
+        <v>826</v>
+      </c>
+      <c r="F127" t="s">
         <v>827</v>
       </c>
-      <c r="B127" t="s">
-        <v>526</v>
-      </c>
-      <c r="C127" t="s">
-        <v>307</v>
-      </c>
-      <c r="D127" t="s">
-        <v>246</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="H127" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="F127" t="s">
-        <v>637</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>829</v>
+      </c>
+      <c r="B128" t="s">
+        <v>526</v>
+      </c>
+      <c r="C128" t="s">
+        <v>307</v>
+      </c>
+      <c r="D128" t="s">
+        <v>246</v>
+      </c>
+      <c r="E128" t="s">
         <v>830</v>
       </c>
-      <c r="B128" t="s">
+      <c r="F128" t="s">
+        <v>639</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="C128" t="s">
-        <v>832</v>
-      </c>
-      <c r="D128" t="s">
-        <v>379</v>
-      </c>
-      <c r="E128" t="s">
-        <v>833</v>
-      </c>
-      <c r="F128" t="s">
-        <v>834</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B129" t="s">
+        <v>833</v>
+      </c>
+      <c r="C129" t="s">
+        <v>834</v>
+      </c>
+      <c r="D129" t="s">
+        <v>379</v>
+      </c>
+      <c r="E129" t="s">
+        <v>835</v>
+      </c>
+      <c r="F129" t="s">
         <v>836</v>
-      </c>
-      <c r="C129" t="s">
-        <v>278</v>
-      </c>
-      <c r="D129" t="s">
-        <v>246</v>
-      </c>
-      <c r="E129" t="s">
-        <v>338</v>
-      </c>
-      <c r="F129" t="s">
-        <v>615</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>837</v>
@@ -7313,68 +7319,68 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B130" t="s">
         <v>838</v>
       </c>
       <c r="C130" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D130" t="s">
         <v>246</v>
       </c>
       <c r="E130" t="s">
+        <v>338</v>
+      </c>
+      <c r="F130" t="s">
+        <v>617</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="F130" t="s">
-        <v>840</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B131" t="s">
+        <v>840</v>
+      </c>
+      <c r="C131" t="s">
+        <v>288</v>
+      </c>
+      <c r="D131" t="s">
+        <v>246</v>
+      </c>
+      <c r="E131" t="s">
+        <v>841</v>
+      </c>
+      <c r="F131" t="s">
         <v>842</v>
       </c>
-      <c r="C131" t="s">
+      <c r="H131" s="2" t="s">
         <v>843</v>
-      </c>
-      <c r="D131" t="s">
-        <v>246</v>
-      </c>
-      <c r="E131" t="s">
-        <v>844</v>
-      </c>
-      <c r="F131" t="s">
-        <v>845</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B132" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C132" t="s">
+        <v>845</v>
+      </c>
+      <c r="D132" t="s">
+        <v>246</v>
+      </c>
+      <c r="E132" t="s">
+        <v>846</v>
+      </c>
+      <c r="F132" t="s">
         <v>847</v>
-      </c>
-      <c r="D132" t="s">
-        <v>246</v>
-      </c>
-      <c r="E132" t="s">
-        <v>844</v>
-      </c>
-      <c r="F132" t="s">
-        <v>845</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>848</v>
@@ -7382,68 +7388,68 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B133" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C133" t="s">
-        <v>296</v>
+        <v>849</v>
       </c>
       <c r="D133" t="s">
         <v>246</v>
       </c>
       <c r="E133" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F133" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
       <c r="B134" t="s">
+        <v>844</v>
+      </c>
+      <c r="C134" t="s">
+        <v>296</v>
+      </c>
+      <c r="D134" t="s">
+        <v>246</v>
+      </c>
+      <c r="E134" t="s">
+        <v>846</v>
+      </c>
+      <c r="F134" t="s">
+        <v>847</v>
+      </c>
+      <c r="H134" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="C134" t="s">
-        <v>852</v>
-      </c>
-      <c r="D134" t="s">
-        <v>246</v>
-      </c>
-      <c r="E134" t="s">
-        <v>853</v>
-      </c>
-      <c r="F134" t="s">
-        <v>854</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>852</v>
+      </c>
+      <c r="B135" t="s">
+        <v>853</v>
+      </c>
+      <c r="C135" t="s">
+        <v>854</v>
+      </c>
+      <c r="D135" t="s">
+        <v>246</v>
+      </c>
+      <c r="E135" t="s">
+        <v>855</v>
+      </c>
+      <c r="F135" t="s">
         <v>856</v>
-      </c>
-      <c r="B135" t="s">
-        <v>851</v>
-      </c>
-      <c r="C135" t="s">
-        <v>278</v>
-      </c>
-      <c r="D135" t="s">
-        <v>246</v>
-      </c>
-      <c r="E135" t="s">
-        <v>853</v>
-      </c>
-      <c r="F135" t="s">
-        <v>854</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>857</v>
@@ -7454,206 +7460,229 @@
         <v>858</v>
       </c>
       <c r="B136" t="s">
+        <v>853</v>
+      </c>
+      <c r="C136" t="s">
+        <v>278</v>
+      </c>
+      <c r="D136" t="s">
+        <v>246</v>
+      </c>
+      <c r="E136" t="s">
+        <v>855</v>
+      </c>
+      <c r="F136" t="s">
+        <v>856</v>
+      </c>
+      <c r="H136" s="2" t="s">
         <v>859</v>
-      </c>
-      <c r="C136" t="s">
-        <v>360</v>
-      </c>
-      <c r="D136" t="s">
-        <v>246</v>
-      </c>
-      <c r="E136" t="s">
-        <v>860</v>
-      </c>
-      <c r="F136" t="s">
-        <v>241</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>860</v>
+      </c>
+      <c r="B137" t="s">
+        <v>861</v>
+      </c>
+      <c r="C137" t="s">
+        <v>360</v>
+      </c>
+      <c r="D137" t="s">
+        <v>246</v>
+      </c>
+      <c r="E137" t="s">
         <v>862</v>
       </c>
-      <c r="B137" t="s">
+      <c r="F137" t="s">
+        <v>241</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="C137" t="s">
-        <v>864</v>
-      </c>
-      <c r="D137" t="s">
-        <v>379</v>
-      </c>
-      <c r="E137" t="s">
-        <v>268</v>
-      </c>
-      <c r="F137" t="s">
-        <v>865</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>864</v>
+      </c>
+      <c r="B138" t="s">
+        <v>865</v>
+      </c>
+      <c r="C138" t="s">
+        <v>866</v>
+      </c>
+      <c r="D138" t="s">
+        <v>379</v>
+      </c>
+      <c r="E138" t="s">
+        <v>268</v>
+      </c>
+      <c r="F138" t="s">
         <v>867</v>
       </c>
-      <c r="B138" t="s">
+      <c r="H138" s="2" t="s">
         <v>868</v>
-      </c>
-      <c r="C138" t="s">
-        <v>288</v>
-      </c>
-      <c r="D138" t="s">
-        <v>246</v>
-      </c>
-      <c r="E138" t="s">
-        <v>869</v>
-      </c>
-      <c r="F138" t="s">
-        <v>339</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>869</v>
+      </c>
+      <c r="B139" t="s">
+        <v>870</v>
+      </c>
+      <c r="C139" t="s">
+        <v>288</v>
+      </c>
+      <c r="D139" t="s">
+        <v>246</v>
+      </c>
+      <c r="E139" t="s">
         <v>871</v>
       </c>
-      <c r="B139" t="s">
-        <v>640</v>
-      </c>
-      <c r="C139" t="s">
-        <v>278</v>
-      </c>
-      <c r="D139" t="s">
-        <v>246</v>
-      </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
+        <v>339</v>
+      </c>
+      <c r="H139" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="F139" t="s">
-        <v>873</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>873</v>
+      </c>
+      <c r="B140" t="s">
+        <v>642</v>
+      </c>
+      <c r="C140" t="s">
+        <v>278</v>
+      </c>
+      <c r="D140" t="s">
+        <v>246</v>
+      </c>
+      <c r="E140" t="s">
+        <v>874</v>
+      </c>
+      <c r="F140" t="s">
         <v>875</v>
       </c>
-      <c r="B140" t="s">
+      <c r="H140" s="2" t="s">
         <v>876</v>
-      </c>
-      <c r="C140" t="s">
-        <v>877</v>
-      </c>
-      <c r="D140" t="s">
-        <v>246</v>
-      </c>
-      <c r="E140" t="s">
-        <v>878</v>
-      </c>
-      <c r="F140" t="s">
-        <v>268</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>877</v>
+      </c>
+      <c r="B141" t="s">
+        <v>878</v>
+      </c>
+      <c r="C141" t="s">
+        <v>879</v>
+      </c>
+      <c r="D141" t="s">
+        <v>246</v>
+      </c>
+      <c r="E141" t="s">
         <v>880</v>
       </c>
-      <c r="B141" t="s">
+      <c r="F141" t="s">
+        <v>268</v>
+      </c>
+      <c r="H141" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="C141" t="s">
-        <v>882</v>
-      </c>
-      <c r="D141" t="s">
-        <v>246</v>
-      </c>
-      <c r="E141" t="s">
-        <v>883</v>
-      </c>
-      <c r="F141" t="s">
-        <v>884</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>882</v>
+      </c>
+      <c r="B142" t="s">
+        <v>883</v>
+      </c>
+      <c r="C142" t="s">
+        <v>884</v>
+      </c>
+      <c r="D142" t="s">
+        <v>246</v>
+      </c>
+      <c r="E142" t="s">
+        <v>885</v>
+      </c>
+      <c r="F142" t="s">
         <v>886</v>
       </c>
-      <c r="B142" t="s">
+      <c r="H142" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="C142" t="s">
-        <v>888</v>
-      </c>
-      <c r="D142" t="s">
-        <v>246</v>
-      </c>
-      <c r="E142" t="s">
-        <v>889</v>
-      </c>
-      <c r="F142" t="s">
-        <v>890</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>888</v>
+      </c>
+      <c r="B143" t="s">
+        <v>889</v>
+      </c>
+      <c r="C143" t="s">
+        <v>890</v>
+      </c>
+      <c r="D143" t="s">
+        <v>246</v>
+      </c>
+      <c r="E143" t="s">
+        <v>891</v>
+      </c>
+      <c r="F143" t="s">
         <v>892</v>
       </c>
-      <c r="B143" t="s">
+      <c r="H143" s="2" t="s">
         <v>893</v>
-      </c>
-      <c r="C143" t="s">
-        <v>894</v>
-      </c>
-      <c r="D143" t="s">
-        <v>246</v>
-      </c>
-      <c r="E143" t="s">
-        <v>676</v>
-      </c>
-      <c r="F143" t="s">
-        <v>895</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>894</v>
+      </c>
+      <c r="B144" t="s">
+        <v>895</v>
+      </c>
+      <c r="C144" t="s">
+        <v>896</v>
+      </c>
+      <c r="D144" t="s">
+        <v>246</v>
+      </c>
+      <c r="E144" t="s">
+        <v>678</v>
+      </c>
+      <c r="F144" t="s">
         <v>897</v>
       </c>
-      <c r="B144" t="s">
+      <c r="H144" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>899</v>
+      </c>
+      <c r="B145" t="s">
         <v>576</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C145" t="s">
         <v>577</v>
       </c>
-      <c r="D144" t="s">
-        <v>246</v>
-      </c>
-      <c r="E144" t="s">
-        <v>898</v>
-      </c>
-      <c r="F144" t="s">
-        <v>899</v>
-      </c>
-      <c r="H144" s="2" t="s">
+      <c r="D145" t="s">
+        <v>246</v>
+      </c>
+      <c r="E145" t="s">
         <v>900</v>
+      </c>
+      <c r="F145" t="s">
+        <v>901</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>902</v>
       </c>
     </row>
   </sheetData>
@@ -7802,6 +7831,7 @@
     <hyperlink ref="H142" r:id="rId141"/>
     <hyperlink ref="H143" r:id="rId142"/>
     <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
